--- a/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
@@ -445,42 +445,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,28 +499,28 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>63.42185589186604</v>
+        <v>642.1425063630761</v>
       </c>
       <c r="D2" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="E2" t="n">
-        <v>65.74149070128979</v>
+        <v>535.2234067931822</v>
       </c>
       <c r="F2" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="G2" t="n">
-        <v>79.17580649646685</v>
+        <v>608.234751973933</v>
       </c>
       <c r="H2" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="I2" t="n">
-        <v>78.58319990692546</v>
+        <v>583.7264349594867</v>
       </c>
       <c r="J2" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="K2" t="n">
         <v>0.003</v>
@@ -536,28 +536,28 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>148.0991910345391</v>
+        <v>777.4937979035642</v>
       </c>
       <c r="D3" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="E3" t="n">
-        <v>146.3777442970684</v>
+        <v>662.9830775275</v>
       </c>
       <c r="F3" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="G3" t="n">
-        <v>162.5327246409163</v>
+        <v>716.2920545273265</v>
       </c>
       <c r="H3" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="I3" t="n">
-        <v>161.0414104606289</v>
+        <v>719.1429938608278</v>
       </c>
       <c r="J3" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="K3" t="n">
         <v>0.003</v>
@@ -573,28 +573,28 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>285.6175218980327</v>
+        <v>783.0089559846165</v>
       </c>
       <c r="D4" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="E4" t="n">
-        <v>284.933964689133</v>
+        <v>671.0644142405843</v>
       </c>
       <c r="F4" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="G4" t="n">
-        <v>293.4767964567177</v>
+        <v>722.6749827633678</v>
       </c>
       <c r="H4" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="I4" t="n">
-        <v>292.9865085524485</v>
+        <v>759.1268288592615</v>
       </c>
       <c r="J4" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="K4" t="n">
         <v>0.003</v>
@@ -610,28 +610,28 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>650.487733852361</v>
+        <v>917.8912060203792</v>
       </c>
       <c r="D5" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="E5" t="n">
-        <v>649.4573496331275</v>
+        <v>934.0867024305651</v>
       </c>
       <c r="F5" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="G5" t="n">
-        <v>607.9893008969213</v>
+        <v>968.4880068431048</v>
       </c>
       <c r="H5" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="I5" t="n">
-        <v>620.9535722674437</v>
+        <v>934.6647870538226</v>
       </c>
       <c r="J5" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="K5" t="n">
         <v>0.003</v>
@@ -647,28 +647,28 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>650.4877338523609</v>
+        <v>917.8912060203792</v>
       </c>
       <c r="D6" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="E6" t="n">
-        <v>650.0174513346574</v>
+        <v>936.3331340492535</v>
       </c>
       <c r="F6" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="G6" t="n">
-        <v>607.9893008969213</v>
+        <v>975.9242960208379</v>
       </c>
       <c r="H6" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="I6" t="n">
-        <v>622.0413321889329</v>
+        <v>935.7357405940484</v>
       </c>
       <c r="J6" t="n">
-        <v>135931.090101806</v>
+        <v>136007.1489410463</v>
       </c>
       <c r="K6" t="n">
         <v>0.003</v>
@@ -687,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>203.8966351527091</v>
+        <v>119.5900790376851</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>203.8966351527091</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>119.5264282781777</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>119.5264282781777</v>
+        <v>119.5900790376851</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -724,25 +724,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>203.8966351527091</v>
+        <v>152.972602329056</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>203.8966351527091</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>152.8890070286202</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>152.8890070286202</v>
+        <v>152.972602329056</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -761,25 +761,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>203.8966351527091</v>
+        <v>167.8392704484934</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>203.8966351527091</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>167.7467929893248</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>167.7467929893248</v>
+        <v>167.8392704484934</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -798,25 +798,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>203.8966351527091</v>
+        <v>175.9858166496768</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>203.8966351527091</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>175.8884719992922</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>175.8884719992922</v>
+        <v>175.9858166496768</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -835,25 +835,25 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>203.8966351527091</v>
+        <v>181.0438694811363</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>203.8966351527091</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>180.9435028739979</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>180.9435028739979</v>
+        <v>181.0438694811363</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -872,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3.470919934350114</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.057189028300619</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.057189028300619</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3.470919934350114</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.569144677828686</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.569144677828686</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.470919934350114</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.866975051233829</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.866975051233829</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -983,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.470919934350114</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.060457132991987</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.060457132991987</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1020,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.470919934350114</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.195880811764982</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.195880811764982</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08077124940774524</v>
+        <v>0.08107694156772063</v>
       </c>
       <c r="D17" t="n">
-        <v>3.470919934350114</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08061497593976577</v>
+        <v>0.08107694156772062</v>
       </c>
       <c r="F17" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G17" t="n">
-        <v>0.080893446900325</v>
+        <v>0.08107694156772063</v>
       </c>
       <c r="H17" t="n">
-        <v>1.057189028300619</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08083243931633535</v>
+        <v>0.08107694156772061</v>
       </c>
       <c r="J17" t="n">
-        <v>1.057189028300619</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08077124940774524</v>
+        <v>0.08176476766181393</v>
       </c>
       <c r="D18" t="n">
-        <v>3.470919934350114</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08061497593976577</v>
+        <v>0.08166422014075095</v>
       </c>
       <c r="F18" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08089344690032503</v>
+        <v>0.08166422014075093</v>
       </c>
       <c r="H18" t="n">
-        <v>1.569144677828686</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08083243931633535</v>
+        <v>0.08176476766181393</v>
       </c>
       <c r="J18" t="n">
-        <v>1.569144677828686</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08163600918417009</v>
+        <v>0.08262513138655603</v>
       </c>
       <c r="D19" t="n">
-        <v>3.470919934350114</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08163600918417009</v>
+        <v>0.08261203023901018</v>
       </c>
       <c r="F19" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08167245557960899</v>
+        <v>0.08261203023901016</v>
       </c>
       <c r="H19" t="n">
-        <v>1.866975051233829</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08171430164745737</v>
+        <v>0.08260826706804172</v>
       </c>
       <c r="J19" t="n">
-        <v>1.866975051233829</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08262513138655601</v>
       </c>
       <c r="D20" t="n">
-        <v>3.470919934350114</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08133311667316744</v>
       </c>
       <c r="F20" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08106090679216499</v>
       </c>
       <c r="H20" t="n">
-        <v>2.060457132991987</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08261203023901018</v>
       </c>
       <c r="J20" t="n">
-        <v>2.060457132991987</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08193730529246272</v>
       </c>
       <c r="D21" t="n">
-        <v>3.470919934350114</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08175126649824412</v>
+        <v>0.08102196079476225</v>
       </c>
       <c r="F21" t="n">
-        <v>3.470919934350114</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0817512664982441</v>
+        <v>0.08076210030521676</v>
       </c>
       <c r="H21" t="n">
-        <v>2.195880811764982</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08175126649824413</v>
+        <v>0.08192420414491686</v>
       </c>
       <c r="J21" t="n">
-        <v>2.195880811764982</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02923531504649207</v>
+        <v>0.02985187893176471</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02898528305540567</v>
+        <v>0.02985187893176471</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02939503192813218</v>
+        <v>0.02985187893176471</v>
       </c>
       <c r="H22" t="n">
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02933745095913385</v>
+        <v>0.02985187893176471</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02933745095913385</v>
+        <v>0.02993724289411765</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02932068673176471</v>
+        <v>0.02993724289411765</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02940605069411765</v>
+        <v>0.02993724289411765</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02933745095913385</v>
+        <v>0.02993724289411765</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0299182344682353</v>
+        <v>0.03188228960470588</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0299182344682353</v>
+        <v>0.03182274634274488</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03027364300470582</v>
+        <v>0.03182274634274488</v>
       </c>
       <c r="H24" t="n">
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03068170667058823</v>
+        <v>0.03180564314823529</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03333258755294118</v>
+        <v>0.03376969828470588</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03333258755294118</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03356029785823583</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03353200706441689</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03333258755294118</v>
+        <v>0.03376969828470588</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03333258755294118</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03356029785823583</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03353200706441689</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.0361830095566004</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0361830095566004</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.06235215139065679</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06235215139065679</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.08284414207442109</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08284414207442109</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.09971239592410397</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09971239592410397</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.1140828146841643</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1140828146841643</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00339846925373222</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="D32" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003391325323767447</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="F32" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00340405542482158</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="H32" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="I32" t="n">
-        <v>0.003401266506696339</v>
+        <v>0.003412443752473951</v>
       </c>
       <c r="J32" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1646,28 +1646,28 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00339846925373222</v>
+        <v>0.003443887231061067</v>
       </c>
       <c r="D33" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003391325323767447</v>
+        <v>0.003439290772955338</v>
       </c>
       <c r="F33" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00340405542482158</v>
+        <v>0.003439290772955337</v>
       </c>
       <c r="H33" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003401266506696339</v>
+        <v>0.003443887231061074</v>
       </c>
       <c r="J33" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="K33" t="n">
         <v>175</v>
@@ -1683,28 +1683,28 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003438001129225927</v>
+        <v>0.003510231617690212</v>
       </c>
       <c r="D34" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003438001129225927</v>
+        <v>0.003497220638844078</v>
       </c>
       <c r="F34" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003439667250160277</v>
+        <v>0.003497220638844079</v>
       </c>
       <c r="H34" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="I34" t="n">
-        <v>0.003441580213261916</v>
+        <v>0.003493483367914731</v>
       </c>
       <c r="J34" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="K34" t="n">
         <v>175</v>
@@ -1720,28 +1720,28 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003941639315975926</v>
       </c>
       <c r="D35" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003904701122929663</v>
       </c>
       <c r="F35" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003933724470534174</v>
+        <v>0.00391714500320406</v>
       </c>
       <c r="H35" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="I35" t="n">
-        <v>0.003927258003375558</v>
+        <v>0.003846236502776852</v>
       </c>
       <c r="J35" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="K35" t="n">
         <v>175</v>
@@ -1757,28 +1757,28 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003973082794563049</v>
       </c>
       <c r="D36" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="E36" t="n">
-        <v>0.003881676400752538</v>
+        <v>0.003918925391656758</v>
       </c>
       <c r="F36" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003933724470534175</v>
+        <v>0.003930804728321693</v>
       </c>
       <c r="H36" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="I36" t="n">
-        <v>0.003927258003375558</v>
+        <v>0.003877679981363975</v>
       </c>
       <c r="J36" t="n">
-        <v>2.330247258888103</v>
+        <v>2.331551124703651</v>
       </c>
       <c r="K36" t="n">
         <v>175</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.008064012787509046</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01414493049880368</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01904648974658279</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02317251719325205</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02674600741059475</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0155450848915837</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0155450848915837</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0272673359013083</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0272673359013083</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.03671612481268972</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03671612481268972</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.04466991266169069</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04466991266169069</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.05155856850235133</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05155856850235133</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0002150403410002412</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0003771981466347649</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0005079063932422078</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2278,19 +2278,19 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0006179337918200545</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.002812259312039597</v>
       </c>
       <c r="F50" t="n">
         <v>0.00752698044642857</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.00270196970049451</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0007132268642825267</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.002812259312039597</v>
       </c>
       <c r="F51" t="n">
         <v>0.00752698044642857</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.00270196970049451</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2719,25 +2719,25 @@
         <v>46023</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="D62" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="F62" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="H62" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="I62" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="J62" t="n">
         <v>1.2868574628</v>
@@ -2756,25 +2756,25 @@
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="D63" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="F63" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="H63" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="I63" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="J63" t="n">
         <v>1.2868574628</v>
@@ -2793,25 +2793,25 @@
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3214643371535644</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="D64" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3108408131935662</v>
+        <v>0.1490189445946008</v>
       </c>
       <c r="F64" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3008389472230494</v>
+        <v>0.1365965460824477</v>
       </c>
       <c r="H64" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="I64" t="n">
-        <v>0.306394634</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="J64" t="n">
         <v>1.2868574628</v>
@@ -2830,7 +2830,7 @@
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.11489798775</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="D65" t="n">
         <v>1.2868574628</v>
@@ -2842,13 +2842,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09070376781244265</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="H65" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="I65" t="n">
-        <v>0.09370966465570502</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="J65" t="n">
         <v>1.2868574628</v>
@@ -2867,7 +2867,7 @@
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.11489798775</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="D66" t="n">
         <v>1.2868574628</v>
@@ -2879,13 +2879,13 @@
         <v>1.2868574628</v>
       </c>
       <c r="G66" t="n">
-        <v>0.09070376781244265</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="H66" t="n">
         <v>1.2868574628</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09370966465570502</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="J66" t="n">
         <v>1.2868574628</v>
@@ -2904,25 +2904,25 @@
         <v>46023</v>
       </c>
       <c r="C67" t="n">
-        <v>2.338846214300958</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="D67" t="n">
         <v>16.519864788</v>
       </c>
       <c r="E67" t="n">
-        <v>2.28323095240921</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="F67" t="n">
         <v>16.519864788</v>
       </c>
       <c r="G67" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408313</v>
       </c>
       <c r="H67" t="n">
         <v>16.519864788</v>
       </c>
       <c r="I67" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="J67" t="n">
         <v>16.519864788</v>
@@ -2941,25 +2941,25 @@
         <v>47849</v>
       </c>
       <c r="C68" t="n">
-        <v>2.338846214300958</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="D68" t="n">
         <v>16.519864788</v>
       </c>
       <c r="E68" t="n">
-        <v>2.28323095240921</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="F68" t="n">
         <v>16.519864788</v>
       </c>
       <c r="G68" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408313</v>
       </c>
       <c r="H68" t="n">
         <v>16.519864788</v>
       </c>
       <c r="I68" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="J68" t="n">
         <v>16.519864788</v>
@@ -2978,25 +2978,25 @@
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>2.338846214300958</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="D69" t="n">
         <v>16.519864788</v>
       </c>
       <c r="E69" t="n">
-        <v>2.28323095240921</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="F69" t="n">
         <v>16.519864788</v>
       </c>
       <c r="G69" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408313</v>
       </c>
       <c r="H69" t="n">
         <v>16.519864788</v>
       </c>
       <c r="I69" t="n">
-        <v>1.703506729362869</v>
+        <v>0.2840693295408315</v>
       </c>
       <c r="J69" t="n">
         <v>16.519864788</v>
@@ -3015,25 +3015,25 @@
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="D70" t="n">
         <v>16.519864788</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="F70" t="n">
         <v>16.519864788</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="H70" t="n">
         <v>16.519864788</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="J70" t="n">
         <v>16.519864788</v>
@@ -3052,25 +3052,25 @@
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="D71" t="n">
         <v>16.519864788</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="F71" t="n">
         <v>16.519864788</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="H71" t="n">
         <v>16.519864788</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3874157745292857</v>
+        <v>0.1537876479167835</v>
       </c>
       <c r="J71" t="n">
         <v>16.519864788</v>
@@ -4569,28 +4569,28 @@
         <v>46023</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>0.8173288823411099</v>
       </c>
       <c r="D112" t="n">
-        <v>29.17576036758886</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.815933588584339</v>
       </c>
       <c r="F112" t="n">
-        <v>29.17576036758886</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.7980446955356428</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>0.8126712660303823</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K112" t="n">
         <v>1</v>
@@ -4606,28 +4606,28 @@
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>1.288702359378202</v>
+        <v>3.928035457318434</v>
       </c>
       <c r="D113" t="n">
-        <v>29.17576036758886</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="E113" t="n">
-        <v>1.292322196915</v>
+        <v>3.8622296382784</v>
       </c>
       <c r="F113" t="n">
-        <v>29.17576036758886</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>3.879135113112059</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>3.934229926809291</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K113" t="n">
         <v>1</v>
@@ -4643,28 +4643,28 @@
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>2.54407371109254</v>
+        <v>4.387016591576031</v>
       </c>
       <c r="D114" t="n">
-        <v>29.17576036758886</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="E114" t="n">
-        <v>2.545220770381199</v>
+        <v>3.949408456660084</v>
       </c>
       <c r="F114" t="n">
-        <v>29.17576036758886</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3.965328962896857</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>4.401427548120806</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K114" t="n">
         <v>1</v>
@@ -4680,28 +4680,28 @@
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>3.177179490049656</v>
+        <v>5.648880524500106</v>
       </c>
       <c r="D115" t="n">
-        <v>29.17576036758886</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="E115" t="n">
-        <v>3.177174898781125</v>
+        <v>3.949408456660084</v>
       </c>
       <c r="F115" t="n">
-        <v>29.17576036758886</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3.965328962896857</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>5.652300669671559</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K115" t="n">
         <v>1</v>
@@ -4717,28 +4717,28 @@
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>3.177179490049656</v>
+        <v>5.752463465642453</v>
       </c>
       <c r="D116" t="n">
-        <v>29.17576036758886</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="E116" t="n">
-        <v>3.177174898781125</v>
+        <v>3.609935756437439</v>
       </c>
       <c r="F116" t="n">
-        <v>29.17576036758886</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3.587500924458367</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>5.776843553250443</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K116" t="n">
         <v>1</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>61.50074829873743</v>
+        <v>33.24393928582102</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>33.24393928582102</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>61.50074829873743</v>
+        <v>43.24534973770062</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>43.24534973770062</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>61.50074829873743</v>
+        <v>48.05024605213596</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>48.05024605213596</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>61.50074829873743</v>
+        <v>50.80548507401782</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>50.80548507401782</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>61.50074829873743</v>
+        <v>52.57001064293669</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>52.57001064293669</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>3.705750567087525</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1.880046910442136</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>3.705750567087525</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>2.526249092198093</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>3.705750567087525</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>2.836698752917273</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.705750567087525</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>3.01471779090852</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.705750567087525</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>3.128725737876166</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5238,19 +5238,19 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>3.03030303030303</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -5275,19 +5275,19 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>3.03030303030303</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5309,28 +5309,28 @@
         <v>46023</v>
       </c>
       <c r="C132" t="n">
-        <v>2.593297499715072</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E132" t="n">
-        <v>5.547142555824531</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G132" t="n">
-        <v>6.208993798639212</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I132" t="n">
-        <v>9.378757273979694</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K132" t="n">
         <v>0.017</v>
@@ -5346,28 +5346,28 @@
         <v>47849</v>
       </c>
       <c r="C133" t="n">
-        <v>2.593297499715072</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E133" t="n">
-        <v>5.558477373659145</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G133" t="n">
-        <v>6.208993798639212</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I133" t="n">
-        <v>9.378757273979694</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K133" t="n">
         <v>0.017</v>
@@ -5383,28 +5383,28 @@
         <v>49675</v>
       </c>
       <c r="C134" t="n">
-        <v>2.593297499715072</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E134" t="n">
-        <v>5.827906028123458</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G134" t="n">
-        <v>6.208993798639212</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I134" t="n">
-        <v>9.658990088105186</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K134" t="n">
         <v>0.017</v>
@@ -5423,25 +5423,25 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E135" t="n">
-        <v>0.280763472298927</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2802328141254928</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K135" t="n">
         <v>0.017</v>
@@ -5460,25 +5460,25 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2694286544643126</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2802328141254928</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K136" t="n">
         <v>0.017</v>
@@ -5494,28 +5494,28 @@
         <v>46023</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2013398184074657</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4090284304735894</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4665131908356118</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5977720877192074</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K137" t="n">
         <v>0.08</v>
@@ -5531,28 +5531,28 @@
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>0.8262653976142558</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E138" t="n">
-        <v>1.024943173328522</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G138" t="n">
-        <v>0.8834946094221606</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I138" t="n">
-        <v>1.04756022588461</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K138" t="n">
         <v>0.08</v>
@@ -5568,28 +5568,28 @@
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>0.8262653976142558</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E139" t="n">
-        <v>1.024943173328522</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8834946094221606</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I139" t="n">
-        <v>1.04756022588461</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K139" t="n">
         <v>0.08</v>
@@ -5605,28 +5605,28 @@
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>0.62492557920679</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E140" t="n">
-        <v>0.6159147428549328</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4169814185865489</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4497881381654028</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K140" t="n">
         <v>0.08</v>
@@ -5645,25 +5645,25 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K141" t="n">
         <v>0.08</v>
@@ -5679,28 +5679,28 @@
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>35.23675532926304</v>
       </c>
       <c r="D142" t="n">
-        <v>152.0470455617122</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>23.28695250889229</v>
       </c>
       <c r="F142" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G142" t="n">
-        <v>16.06353749271533</v>
+        <v>20.70736539500782</v>
       </c>
       <c r="H142" t="n">
-        <v>46.05570405285701</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I142" t="n">
-        <v>13.05807217948053</v>
+        <v>36.51427447413628</v>
       </c>
       <c r="J142" t="n">
-        <v>46.05570405285701</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="K142" t="n">
         <v>0.017</v>
@@ -5716,28 +5716,28 @@
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>35.23675532926304</v>
       </c>
       <c r="D143" t="n">
-        <v>152.0470455617122</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>23.41282014156247</v>
       </c>
       <c r="F143" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G143" t="n">
-        <v>16.06353749271533</v>
+        <v>21.19061490961451</v>
       </c>
       <c r="H143" t="n">
-        <v>64.63354159131777</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I143" t="n">
-        <v>13.05807217948053</v>
+        <v>36.51427447413628</v>
       </c>
       <c r="J143" t="n">
-        <v>64.63354159131777</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="K143" t="n">
         <v>0.017</v>
@@ -5753,28 +5753,28 @@
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>10.52086161952298</v>
+        <v>45.30495501606957</v>
       </c>
       <c r="D144" t="n">
-        <v>152.0470455617122</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="E144" t="n">
-        <v>10.08889555451101</v>
+        <v>35.09786622765415</v>
       </c>
       <c r="F144" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G144" t="n">
-        <v>26.27479709427987</v>
+        <v>32.74837177362869</v>
       </c>
       <c r="H144" t="n">
-        <v>75.28502041326695</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I144" t="n">
-        <v>22.74909599824281</v>
+        <v>47.39878685835764</v>
       </c>
       <c r="J144" t="n">
-        <v>75.28502041326695</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="K144" t="n">
         <v>0.017</v>
@@ -5790,28 +5790,28 @@
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>38.68465153658674</v>
+        <v>48.53179471885529</v>
       </c>
       <c r="D145" t="n">
-        <v>152.0470455617122</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="E145" t="n">
-        <v>37.61513868177823</v>
+        <v>50.76838981472233</v>
       </c>
       <c r="F145" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G145" t="n">
-        <v>38.50507571540649</v>
+        <v>49.80524470800641</v>
       </c>
       <c r="H145" t="n">
-        <v>82.13824663771003</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I145" t="n">
-        <v>37.039659193893</v>
+        <v>50.2689129275973</v>
       </c>
       <c r="J145" t="n">
-        <v>82.13824663771003</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="K145" t="n">
         <v>0.017</v>
@@ -5827,28 +5827,28 @@
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>38.68465153658674</v>
+        <v>48.53179471885529</v>
       </c>
       <c r="D146" t="n">
-        <v>152.0470455617122</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="E146" t="n">
-        <v>37.61513868177823</v>
+        <v>50.64252218205215</v>
       </c>
       <c r="F146" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G146" t="n">
-        <v>38.50507571540649</v>
+        <v>49.32199519339973</v>
       </c>
       <c r="H146" t="n">
-        <v>86.90219116839839</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I146" t="n">
-        <v>37.039659193893</v>
+        <v>50.2689129275973</v>
       </c>
       <c r="J146" t="n">
-        <v>86.90219116839839</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="K146" t="n">
         <v>0.017</v>
@@ -5864,28 +5864,28 @@
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>0.9745343041553989</v>
       </c>
       <c r="D147" t="n">
-        <v>9.109003245912584</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1.139805678462902</v>
       </c>
       <c r="F147" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1672466948049194</v>
+        <v>0.9647126967907047</v>
       </c>
       <c r="H147" t="n">
-        <v>2.454243728747179</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1.137324415846374</v>
       </c>
       <c r="J147" t="n">
-        <v>2.454243728747179</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="K147" t="n">
         <v>0.08</v>
@@ -5901,28 +5901,28 @@
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>1.038145263927251</v>
+        <v>2.873579449874479</v>
       </c>
       <c r="D148" t="n">
-        <v>9.109003245912584</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="E148" t="n">
-        <v>1.058378259260321</v>
+        <v>2.968197968865652</v>
       </c>
       <c r="F148" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G148" t="n">
-        <v>1.242631229443763</v>
+        <v>2.846595129892914</v>
       </c>
       <c r="H148" t="n">
-        <v>3.620669583986453</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I148" t="n">
-        <v>1.049568350280087</v>
+        <v>2.973780062832532</v>
       </c>
       <c r="J148" t="n">
-        <v>3.620669583986453</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="K148" t="n">
         <v>0.08</v>
@@ -5938,28 +5938,28 @@
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>1.424446392536133</v>
+        <v>2.980312443430628</v>
       </c>
       <c r="D149" t="n">
-        <v>9.109003245912584</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="E149" t="n">
-        <v>1.436570648698661</v>
+        <v>3.077189268401386</v>
       </c>
       <c r="F149" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G149" t="n">
-        <v>1.644757352233743</v>
+        <v>2.968646412586611</v>
       </c>
       <c r="H149" t="n">
-        <v>4.289432041873921</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I149" t="n">
-        <v>1.482668467366361</v>
+        <v>3.060045500198731</v>
       </c>
       <c r="J149" t="n">
-        <v>4.289432041873921</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="K149" t="n">
         <v>0.08</v>
@@ -5975,28 +5975,28 @@
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>2.191551223467769</v>
+        <v>3.198323525649897</v>
       </c>
       <c r="D150" t="n">
-        <v>9.109003245912584</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="E150" t="n">
-        <v>2.1268967932664</v>
+        <v>3.332371178024898</v>
       </c>
       <c r="F150" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G150" t="n">
-        <v>2.139915467628115</v>
+        <v>3.23971841641166</v>
       </c>
       <c r="H150" t="n">
-        <v>4.719717872689544</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I150" t="n">
-        <v>2.035767947295985</v>
+        <v>3.269736036639328</v>
       </c>
       <c r="J150" t="n">
-        <v>4.719717872689544</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="K150" t="n">
         <v>0.08</v>
@@ -6012,28 +6012,28 @@
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>2.389349086047102</v>
+        <v>3.058829379926089</v>
       </c>
       <c r="D151" t="n">
-        <v>9.109003245912584</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="E151" t="n">
-        <v>2.356363353515988</v>
+        <v>3.270842222678461</v>
       </c>
       <c r="F151" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G151" t="n">
-        <v>2.393154694391755</v>
+        <v>3.196804501008751</v>
       </c>
       <c r="H151" t="n">
-        <v>5.018826316393861</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I151" t="n">
-        <v>2.354388135514639</v>
+        <v>3.202184544173091</v>
       </c>
       <c r="J151" t="n">
-        <v>5.018826316393861</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="K151" t="n">
         <v>0.08</v>
@@ -6052,25 +6052,25 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>152.0470455617122</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>46.05570405285701</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>46.05570405285701</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="K152" t="n">
         <v>0.017</v>
@@ -6089,25 +6089,25 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>152.0470455617122</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>64.63354159131777</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>64.63354159131777</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="K153" t="n">
         <v>0.017</v>
@@ -6126,25 +6126,25 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>152.0470455617122</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>75.28502041326695</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>75.28502041326695</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="K154" t="n">
         <v>0.017</v>
@@ -6163,25 +6163,25 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>152.0470455617122</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>82.13824663771003</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>82.13824663771003</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="K155" t="n">
         <v>0.017</v>
@@ -6200,25 +6200,25 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>152.0470455617122</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>86.90219116839839</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>86.90219116839839</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="K156" t="n">
         <v>0.017</v>
@@ -6237,25 +6237,25 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>9.109003245912584</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>2.454243728747179</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>2.454243728747179</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="K157" t="n">
         <v>0.08</v>
@@ -6274,25 +6274,25 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>9.109003245912584</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>3.620669583986453</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>3.620669583986453</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="K158" t="n">
         <v>0.08</v>
@@ -6311,25 +6311,25 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>9.109003245912584</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>4.289432041873921</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>4.289432041873921</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="K159" t="n">
         <v>0.08</v>
@@ -6348,25 +6348,25 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>9.109003245912584</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>4.719717872689544</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>4.719717872689544</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="K160" t="n">
         <v>0.08</v>
@@ -6385,25 +6385,25 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>9.109003245912584</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>5.018826316393861</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>5.018826316393861</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="K161" t="n">
         <v>0.08</v>
@@ -6419,28 +6419,28 @@
         <v>46023</v>
       </c>
       <c r="C162" t="n">
-        <v>22.19741895657683</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E162" t="n">
-        <v>22.19114253958764</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G162" t="n">
-        <v>22.17796777440213</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I162" t="n">
-        <v>22.01366961229644</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K162" t="n">
         <v>0.017</v>
@@ -6456,28 +6456,28 @@
         <v>47849</v>
       </c>
       <c r="C163" t="n">
-        <v>22.19741895657683</v>
+        <v>0.1852798886692245</v>
       </c>
       <c r="D163" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E163" t="n">
-        <v>22.19114253958764</v>
+        <v>0.1457412001244685</v>
       </c>
       <c r="F163" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G163" t="n">
-        <v>22.17796777440213</v>
+        <v>0.1852798886692246</v>
       </c>
       <c r="H163" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I163" t="n">
-        <v>22.01366961229644</v>
+        <v>0.1173931149123253</v>
       </c>
       <c r="J163" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K163" t="n">
         <v>0.017</v>
@@ -6493,28 +6493,28 @@
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>24.72318801755641</v>
+        <v>17.85889358704591</v>
       </c>
       <c r="D164" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E164" t="n">
-        <v>24.82682738717769</v>
+        <v>16.14590161762709</v>
       </c>
       <c r="F164" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G164" t="n">
-        <v>24.76152139019803</v>
+        <v>16.35019442112522</v>
       </c>
       <c r="H164" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I164" t="n">
-        <v>24.64862718627786</v>
+        <v>16.21435565446135</v>
       </c>
       <c r="J164" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K164" t="n">
         <v>0.017</v>
@@ -6530,28 +6530,28 @@
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>18.67875579089368</v>
+        <v>18.96723235671676</v>
       </c>
       <c r="D165" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E165" t="n">
-        <v>19.45018492510835</v>
+        <v>16.14590161762709</v>
       </c>
       <c r="F165" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G165" t="n">
-        <v>19.78679201881776</v>
+        <v>16.35019442112522</v>
       </c>
       <c r="H165" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I165" t="n">
-        <v>20.47563795397216</v>
+        <v>16.72398495321817</v>
       </c>
       <c r="J165" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K165" t="n">
         <v>0.017</v>
@@ -6567,28 +6567,28 @@
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>18.67875579089368</v>
+        <v>33.31740000858891</v>
       </c>
       <c r="D166" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E166" t="n">
-        <v>19.71859321281471</v>
+        <v>30.57238326352189</v>
       </c>
       <c r="F166" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G166" t="n">
-        <v>19.78679201881776</v>
+        <v>31.01957579691877</v>
       </c>
       <c r="H166" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I166" t="n">
-        <v>20.73187606394715</v>
+        <v>31.12513057682317</v>
       </c>
       <c r="J166" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K166" t="n">
         <v>0.017</v>
@@ -6604,28 +6604,28 @@
         <v>46023</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3023146725285634</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3023146725285632</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G167" t="n">
-        <v>0.322047023434721</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3580348213560448</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K167" t="n">
         <v>0.08</v>
@@ -6641,28 +6641,28 @@
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>0.3023146725285634</v>
+        <v>0.460493929382878</v>
       </c>
       <c r="D168" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3023146725285632</v>
+        <v>0.4441377190821189</v>
       </c>
       <c r="F168" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G168" t="n">
-        <v>0.322047023434721</v>
+        <v>0.4965511770593832</v>
       </c>
       <c r="H168" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3580348213560448</v>
+        <v>0.403622706582872</v>
       </c>
       <c r="J168" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K168" t="n">
         <v>0.08</v>
@@ -6678,28 +6678,28 @@
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>0.8918743144321275</v>
+        <v>1.353760935826729</v>
       </c>
       <c r="D169" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E169" t="n">
-        <v>0.8922280365446449</v>
+        <v>1.335146419546385</v>
       </c>
       <c r="F169" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G169" t="n">
-        <v>0.8918743144321277</v>
+        <v>1.374499894365686</v>
       </c>
       <c r="H169" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8898975828370594</v>
+        <v>1.317357269216672</v>
       </c>
       <c r="J169" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K169" t="n">
         <v>0.08</v>
@@ -6715,28 +6715,28 @@
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>1.066529616637813</v>
+        <v>1.477678059668234</v>
       </c>
       <c r="D170" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E170" t="n">
-        <v>1.140194883191039</v>
+        <v>1.391970342055296</v>
       </c>
       <c r="F170" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G170" t="n">
-        <v>1.136739993085692</v>
+        <v>1.484623103668534</v>
       </c>
       <c r="H170" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I170" t="n">
-        <v>1.21040703410863</v>
+        <v>1.419338927757271</v>
       </c>
       <c r="J170" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K170" t="n">
         <v>0.08</v>
@@ -6752,28 +6752,28 @@
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>1.49365733326527</v>
+        <v>2.455052416054516</v>
       </c>
       <c r="D171" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E171" t="n">
-        <v>1.526643065796384</v>
+        <v>2.291379508064205</v>
       </c>
       <c r="F171" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G171" t="n">
-        <v>1.470480563496041</v>
+        <v>2.365417229733916</v>
       </c>
       <c r="H171" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I171" t="n">
-        <v>1.511573362642819</v>
+        <v>2.324770630885982</v>
       </c>
       <c r="J171" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K171" t="n">
         <v>0.08</v>
@@ -6792,25 +6792,25 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K172" t="n">
         <v>0.017</v>
@@ -6829,25 +6829,25 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K173" t="n">
         <v>0.017</v>
@@ -6866,25 +6866,25 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K174" t="n">
         <v>0.017</v>
@@ -6903,25 +6903,25 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K175" t="n">
         <v>0.017</v>
@@ -6940,25 +6940,25 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K176" t="n">
         <v>0.017</v>
@@ -6977,25 +6977,25 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K177" t="n">
         <v>0.08</v>
@@ -7014,25 +7014,25 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K178" t="n">
         <v>0.08</v>
@@ -7051,25 +7051,25 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K179" t="n">
         <v>0.08</v>
@@ -7088,25 +7088,25 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K180" t="n">
         <v>0.08</v>
@@ -7125,25 +7125,25 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K181" t="n">
         <v>0.08</v>
@@ -7162,25 +7162,25 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>152.0470455617122</v>
+        <v>10.40759867266749</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>11.37055743557585</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>11.37055743557585</v>
+        <v>10.40759867266749</v>
       </c>
       <c r="K182" t="n">
         <v>0.017</v>
@@ -7199,25 +7199,25 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>152.0470455617122</v>
+        <v>13.30840288608646</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>14.42522800699697</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>14.42522800699697</v>
+        <v>13.30840288608646</v>
       </c>
       <c r="K183" t="n">
         <v>0.017</v>
@@ -7236,25 +7236,25 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>152.0470455617122</v>
+        <v>15.55001026864869</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>16.78573619728351</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>16.78573619728351</v>
+        <v>15.55001026864869</v>
       </c>
       <c r="K184" t="n">
         <v>0.017</v>
@@ -7273,25 +7273,25 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>152.0470455617122</v>
+        <v>17.3724404785241</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>18.70483294460032</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>18.70483294460032</v>
+        <v>17.3724404785241</v>
       </c>
       <c r="K185" t="n">
         <v>0.017</v>
@@ -7310,25 +7310,25 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>152.0470455617122</v>
+        <v>18.9021256255163</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>20.31565665357091</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>20.31565665357091</v>
+        <v>18.9021256255163</v>
       </c>
       <c r="K186" t="n">
         <v>0.017</v>
@@ -7347,25 +7347,25 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>9.109003245912584</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>0.2765063185989636</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0.2765063185989636</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="K187" t="n">
         <v>0.08</v>
@@ -7384,25 +7384,25 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>9.109003245912584</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0.4682964947358649</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0.4682964947358649</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="K188" t="n">
         <v>0.08</v>
@@ -7421,25 +7421,25 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>9.109003245912584</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0.6165030757738437</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0.6165030757738437</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="K189" t="n">
         <v>0.08</v>
@@ -7458,25 +7458,25 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7369952514719948</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.7369952514719948</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="K190" t="n">
         <v>0.08</v>
@@ -7495,25 +7495,25 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>0.838132233560783</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>0.838132233560783</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="K191" t="n">
         <v>0.08</v>
@@ -7529,28 +7529,28 @@
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>25.17874540696422</v>
+        <v>5.251916210523669</v>
       </c>
       <c r="D192" t="n">
-        <v>152.0470455617122</v>
+        <v>10.40759867266749</v>
       </c>
       <c r="E192" t="n">
-        <v>22.23117676784394</v>
+        <v>19.47248582655308</v>
       </c>
       <c r="F192" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G192" t="n">
-        <v>5.51896279749945</v>
+        <v>20.47921905378368</v>
       </c>
       <c r="H192" t="n">
-        <v>11.37055743557585</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I192" t="n">
-        <v>5.51896279749945</v>
+        <v>5.251916210523669</v>
       </c>
       <c r="J192" t="n">
-        <v>11.37055743557585</v>
+        <v>10.40759867266749</v>
       </c>
       <c r="K192" t="n">
         <v>0.017</v>
@@ -7566,28 +7566,28 @@
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>25.17874540696422</v>
+        <v>5.251916210523669</v>
       </c>
       <c r="D193" t="n">
-        <v>152.0470455617122</v>
+        <v>13.30840288608646</v>
       </c>
       <c r="E193" t="n">
-        <v>22.23117676784394</v>
+        <v>19.47248582655308</v>
       </c>
       <c r="F193" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G193" t="n">
-        <v>5.51896279749945</v>
+        <v>20.47921905378368</v>
       </c>
       <c r="H193" t="n">
-        <v>14.42522800699697</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I193" t="n">
-        <v>5.51896279749945</v>
+        <v>5.326518157408448</v>
       </c>
       <c r="J193" t="n">
-        <v>14.42522800699697</v>
+        <v>13.30840288608646</v>
       </c>
       <c r="K193" t="n">
         <v>0.017</v>
@@ -7603,28 +7603,28 @@
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>25.18723821019277</v>
+        <v>5.251916210523669</v>
       </c>
       <c r="D194" t="n">
-        <v>152.0470455617122</v>
+        <v>15.55001026864869</v>
       </c>
       <c r="E194" t="n">
-        <v>22.27971888302697</v>
+        <v>19.47248582655308</v>
       </c>
       <c r="F194" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G194" t="n">
-        <v>5.627619033528643</v>
+        <v>20.47921905378368</v>
       </c>
       <c r="H194" t="n">
-        <v>16.78573619728351</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I194" t="n">
-        <v>5.827033218378772</v>
+        <v>5.326518157408448</v>
       </c>
       <c r="J194" t="n">
-        <v>16.78573619728351</v>
+        <v>15.55001026864869</v>
       </c>
       <c r="K194" t="n">
         <v>0.017</v>
@@ -7640,28 +7640,28 @@
         <v>51502</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00849280322855109</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>152.0470455617122</v>
+        <v>17.3724404785241</v>
       </c>
       <c r="E195" t="n">
-        <v>0.04854211518302505</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G195" t="n">
-        <v>0.108656236029193</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>18.70483294460032</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3080704208793226</v>
+        <v>0.07460194688477868</v>
       </c>
       <c r="J195" t="n">
-        <v>18.70483294460032</v>
+        <v>17.3724404785241</v>
       </c>
       <c r="K195" t="n">
         <v>0.017</v>
@@ -7677,28 +7677,28 @@
         <v>53328</v>
       </c>
       <c r="C196" t="n">
-        <v>0.00849280322855109</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>152.0470455617122</v>
+        <v>18.9021256255163</v>
       </c>
       <c r="E196" t="n">
-        <v>0.04854211518302505</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>152.0470455617122</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G196" t="n">
-        <v>0.108656236029193</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>20.31565665357091</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3080704208793225</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>20.31565665357091</v>
+        <v>18.9021256255163</v>
       </c>
       <c r="K196" t="n">
         <v>0.017</v>
@@ -7714,28 +7714,28 @@
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="D197" t="n">
-        <v>9.109003245912584</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="E197" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="F197" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3724014066674143</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="H197" t="n">
-        <v>0.2765063185989636</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3724014066674143</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="J197" t="n">
-        <v>0.2765063185989636</v>
+        <v>0.2631269806022396</v>
       </c>
       <c r="K197" t="n">
         <v>0.08</v>
@@ -7751,28 +7751,28 @@
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="D198" t="n">
-        <v>9.109003245912584</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="E198" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="F198" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G198" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="H198" t="n">
-        <v>0.4682964947358649</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="J198" t="n">
-        <v>0.4682964947358649</v>
+        <v>0.445636986926065</v>
       </c>
       <c r="K198" t="n">
         <v>0.08</v>
@@ -7788,28 +7788,28 @@
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0.8245538248066371</v>
+        <v>0.3543819837641523</v>
       </c>
       <c r="D199" t="n">
-        <v>9.109003245912584</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="E199" t="n">
-        <v>0.6168652127405144</v>
+        <v>0.312005832132422</v>
       </c>
       <c r="F199" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G199" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3811952131278954</v>
       </c>
       <c r="H199" t="n">
-        <v>0.6165030757738437</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5423997852548543</v>
+        <v>0.3116721949811959</v>
       </c>
       <c r="J199" t="n">
-        <v>0.6165030757738437</v>
+        <v>0.5866722817847868</v>
       </c>
       <c r="K199" t="n">
         <v>0.08</v>
@@ -7828,25 +7828,25 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G200" t="n">
-        <v>0.16999837858744</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7369952514719948</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I200" t="n">
-        <v>0.16999837858744</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0.7369952514719948</v>
+        <v>0.7013341909168983</v>
       </c>
       <c r="K200" t="n">
         <v>0.08</v>
@@ -7865,25 +7865,25 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>9.109003245912584</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>9.109003245912584</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>0.838132233560783</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>0.838132233560783</v>
+        <v>0.7975774480659066</v>
       </c>
       <c r="K201" t="n">
         <v>0.08</v>
@@ -7902,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -7914,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>

--- a/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
@@ -445,32 +445,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -499,19 +499,19 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>642.1425063630761</v>
+        <v>535.2234067931822</v>
       </c>
       <c r="D2" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E2" t="n">
-        <v>535.2234067931822</v>
+        <v>608.234751973933</v>
       </c>
       <c r="F2" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G2" t="n">
-        <v>608.234751973933</v>
+        <v>642.1425063630761</v>
       </c>
       <c r="H2" t="n">
         <v>136007.1489410463</v>
@@ -536,19 +536,19 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>777.4937979035642</v>
+        <v>662.9830775275</v>
       </c>
       <c r="D3" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E3" t="n">
-        <v>662.9830775275</v>
+        <v>716.2920545273265</v>
       </c>
       <c r="F3" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G3" t="n">
-        <v>716.2920545273265</v>
+        <v>777.4937979035642</v>
       </c>
       <c r="H3" t="n">
         <v>136007.1489410463</v>
@@ -573,19 +573,19 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>783.0089559846165</v>
+        <v>671.0644142405843</v>
       </c>
       <c r="D4" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E4" t="n">
-        <v>671.0644142405843</v>
+        <v>722.6749827633678</v>
       </c>
       <c r="F4" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G4" t="n">
-        <v>722.6749827633678</v>
+        <v>783.0089559846165</v>
       </c>
       <c r="H4" t="n">
         <v>136007.1489410463</v>
@@ -610,19 +610,19 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>917.8912060203792</v>
+        <v>934.0867024305651</v>
       </c>
       <c r="D5" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E5" t="n">
-        <v>934.0867024305651</v>
+        <v>968.4880068431048</v>
       </c>
       <c r="F5" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G5" t="n">
-        <v>968.4880068431048</v>
+        <v>917.8912060203792</v>
       </c>
       <c r="H5" t="n">
         <v>136007.1489410463</v>
@@ -647,19 +647,19 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>917.8912060203792</v>
+        <v>936.3331340492535</v>
       </c>
       <c r="D6" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E6" t="n">
-        <v>936.3331340492535</v>
+        <v>975.9242960208379</v>
       </c>
       <c r="F6" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G6" t="n">
-        <v>975.9242960208379</v>
+        <v>917.8912060203792</v>
       </c>
       <c r="H6" t="n">
         <v>136007.1489410463</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>119.5900790376851</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>204.0107234115695</v>
+        <v>119.5900790376851</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>152.972602329056</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>204.0107234115695</v>
+        <v>152.972602329056</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>167.8392704484934</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>204.0107234115695</v>
+        <v>167.8392704484934</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9858166496768</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>204.0107234115695</v>
+        <v>175.9858166496768</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>181.0438694811363</v>
+        <v>204.0107234115695</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>204.0107234115695</v>
+        <v>181.0438694811363</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.002774612488435</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.29226874189296</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1.488379470582734</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.29226874189296</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.770880262100316</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.29226874189296</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.954403657032222</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.29226874189296</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2.082856964215745</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.29226874189296</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1054,13 +1054,13 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
+        <v>0.08107694156772062</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.29226874189296</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.08107694156772063</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.002774612488435</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.08107694156772062</v>
       </c>
       <c r="F17" t="n">
         <v>3.29226874189296</v>
@@ -1069,7 +1069,7 @@
         <v>0.08107694156772063</v>
       </c>
       <c r="H17" t="n">
-        <v>3.29226874189296</v>
+        <v>1.002774612488435</v>
       </c>
       <c r="I17" t="n">
         <v>0.08107694156772061</v>
@@ -1091,22 +1091,22 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08176476766181393</v>
+        <v>0.08166422014075095</v>
       </c>
       <c r="D18" t="n">
-        <v>1.488379470582734</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08166422014075095</v>
+        <v>0.08166422014075093</v>
       </c>
       <c r="F18" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08166422014075093</v>
+        <v>0.08176476766181393</v>
       </c>
       <c r="H18" t="n">
-        <v>3.29226874189296</v>
+        <v>1.488379470582734</v>
       </c>
       <c r="I18" t="n">
         <v>0.08176476766181393</v>
@@ -1128,22 +1128,22 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08262513138655603</v>
+        <v>0.08261203023901018</v>
       </c>
       <c r="D19" t="n">
-        <v>1.770880262100316</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08261203023901018</v>
+        <v>0.08261203023901016</v>
       </c>
       <c r="F19" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08261203023901016</v>
+        <v>0.08262513138655603</v>
       </c>
       <c r="H19" t="n">
-        <v>3.29226874189296</v>
+        <v>1.770880262100316</v>
       </c>
       <c r="I19" t="n">
         <v>0.08260826706804172</v>
@@ -1165,22 +1165,22 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08262513138655601</v>
+        <v>0.08133311667316744</v>
       </c>
       <c r="D20" t="n">
-        <v>1.954403657032222</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08133311667316744</v>
+        <v>0.08106090679216499</v>
       </c>
       <c r="F20" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08106090679216499</v>
+        <v>0.08262513138655601</v>
       </c>
       <c r="H20" t="n">
-        <v>3.29226874189296</v>
+        <v>1.954403657032222</v>
       </c>
       <c r="I20" t="n">
         <v>0.08261203023901018</v>
@@ -1202,22 +1202,22 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08193730529246272</v>
+        <v>0.08102196079476225</v>
       </c>
       <c r="D21" t="n">
-        <v>2.082856964215745</v>
+        <v>3.29226874189296</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08102196079476225</v>
+        <v>0.08076210030521676</v>
       </c>
       <c r="F21" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08076210030521676</v>
+        <v>0.08193730529246272</v>
       </c>
       <c r="H21" t="n">
-        <v>3.29226874189296</v>
+        <v>2.082856964215745</v>
       </c>
       <c r="I21" t="n">
         <v>0.08192420414491686</v>
@@ -1313,7 +1313,7 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.03188228960470588</v>
+        <v>0.03182274634274488</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -1325,7 +1325,7 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03182274634274488</v>
+        <v>0.03188228960470588</v>
       </c>
       <c r="H24" t="n">
         <v>4</v>
@@ -1350,7 +1350,7 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03376969828470588</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1362,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.03376969828470588</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
@@ -1387,7 +1387,7 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03376969828470588</v>
+        <v>0.03334969074745076</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
@@ -1399,7 +1399,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.03376969828470588</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0361830095566004</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.0361830095566004</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.06235215139065679</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.06235215139065679</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08284414207442109</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.08284414207442109</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09971239592410397</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.09971239592410397</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1140828146841643</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.1140828146841643</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1646,19 +1646,19 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003443887231061067</v>
+        <v>0.003439290772955338</v>
       </c>
       <c r="D33" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003439290772955338</v>
+        <v>0.003439290772955337</v>
       </c>
       <c r="F33" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003439290772955337</v>
+        <v>0.003443887231061067</v>
       </c>
       <c r="H33" t="n">
         <v>2.331551124703651</v>
@@ -1683,19 +1683,19 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003510231617690212</v>
+        <v>0.003497220638844078</v>
       </c>
       <c r="D34" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003497220638844078</v>
+        <v>0.003497220638844079</v>
       </c>
       <c r="F34" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003497220638844079</v>
+        <v>0.003510231617690212</v>
       </c>
       <c r="H34" t="n">
         <v>2.331551124703651</v>
@@ -1720,19 +1720,19 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003941639315975926</v>
+        <v>0.003904701122929663</v>
       </c>
       <c r="D35" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003904701122929663</v>
+        <v>0.00391714500320406</v>
       </c>
       <c r="F35" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00391714500320406</v>
+        <v>0.003941639315975926</v>
       </c>
       <c r="H35" t="n">
         <v>2.331551124703651</v>
@@ -1757,19 +1757,19 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003973082794563049</v>
+        <v>0.003918925391656758</v>
       </c>
       <c r="D36" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E36" t="n">
-        <v>0.003918925391656758</v>
+        <v>0.003930804728321693</v>
       </c>
       <c r="F36" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003930804728321693</v>
+        <v>0.003973082794563049</v>
       </c>
       <c r="H36" t="n">
         <v>2.331551124703651</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.008064012787509046</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01414493049880368</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.01904648974658279</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02317251719325205</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.2822617667410714</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.02674600741059475</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0155450848915837</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0155450848915837</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0272673359013083</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.0272673359013083</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03671612481268972</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.03671612481268972</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.04466991266169069</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.04466991266169069</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.05155856850235133</v>
+        <v>0.5441190684165231</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5441190684165231</v>
+        <v>0.05155856850235133</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.002150403410002412</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0002150403410002412</v>
+        <v>0.002150403410002412</v>
       </c>
       <c r="K47" t="n">
         <v>300</v>
@@ -2204,25 +2204,25 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.003771981466347649</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0003771981466347649</v>
+        <v>0.003771981466347649</v>
       </c>
       <c r="K48" t="n">
         <v>300</v>
@@ -2241,25 +2241,25 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.005079063932422078</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0005079063932422078</v>
+        <v>0.005079063932422078</v>
       </c>
       <c r="K49" t="n">
         <v>300</v>
@@ -2275,28 +2275,28 @@
         <v>51502</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.02812259312039597</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="E50" t="n">
-        <v>0.002812259312039597</v>
+        <v>0.0270196970049451</v>
       </c>
       <c r="F50" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00270196970049451</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.006179337918200545</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0006179337918200545</v>
+        <v>0.006179337918200545</v>
       </c>
       <c r="K50" t="n">
         <v>300</v>
@@ -2312,28 +2312,28 @@
         <v>53328</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.02812259312039597</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="E51" t="n">
-        <v>0.002812259312039597</v>
+        <v>0.0270196970049451</v>
       </c>
       <c r="F51" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.0752698044642857</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00270196970049451</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00752698044642857</v>
+        <v>0.007132268642825267</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0007132268642825267</v>
+        <v>0.007132268642825267</v>
       </c>
       <c r="K51" t="n">
         <v>300</v>
@@ -2719,19 +2719,19 @@
         <v>46023</v>
       </c>
       <c r="C62" t="n">
+        <v>0.1490189445946008</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1365965460824477</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="G62" t="n">
         <v>0.1148979877499999</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.1490189445946008</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.1365965460824477</v>
       </c>
       <c r="H62" t="n">
         <v>1.2868574628</v>
@@ -2756,19 +2756,19 @@
         <v>47849</v>
       </c>
       <c r="C63" t="n">
+        <v>0.1490189445946008</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1365965460824477</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="G63" t="n">
         <v>0.1148979877499999</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.1490189445946008</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.1365965460824477</v>
       </c>
       <c r="H63" t="n">
         <v>1.2868574628</v>
@@ -2793,19 +2793,19 @@
         <v>49675</v>
       </c>
       <c r="C64" t="n">
+        <v>0.1490189445946008</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.1365965460824477</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.2868574628</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.1148979877499999</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.1490189445946008</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1.2868574628</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.1365965460824477</v>
       </c>
       <c r="H64" t="n">
         <v>1.2868574628</v>
@@ -2830,7 +2830,7 @@
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="D65" t="n">
         <v>1.2868574628</v>
@@ -2842,7 +2842,7 @@
         <v>1.2868574628</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="H65" t="n">
         <v>1.2868574628</v>
@@ -2867,7 +2867,7 @@
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07659865849999996</v>
+        <v>0.1148979877499999</v>
       </c>
       <c r="D66" t="n">
         <v>1.2868574628</v>
@@ -2879,7 +2879,7 @@
         <v>1.2868574628</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1148979877499999</v>
+        <v>0.07659865849999996</v>
       </c>
       <c r="H66" t="n">
         <v>1.2868574628</v>
@@ -2910,13 +2910,13 @@
         <v>16.519864788</v>
       </c>
       <c r="E67" t="n">
+        <v>0.2840693295408313</v>
+      </c>
+      <c r="F67" t="n">
+        <v>16.519864788</v>
+      </c>
+      <c r="G67" t="n">
         <v>0.2840693295408315</v>
-      </c>
-      <c r="F67" t="n">
-        <v>16.519864788</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.2840693295408313</v>
       </c>
       <c r="H67" t="n">
         <v>16.519864788</v>
@@ -2947,13 +2947,13 @@
         <v>16.519864788</v>
       </c>
       <c r="E68" t="n">
+        <v>0.2840693295408313</v>
+      </c>
+      <c r="F68" t="n">
+        <v>16.519864788</v>
+      </c>
+      <c r="G68" t="n">
         <v>0.2840693295408315</v>
-      </c>
-      <c r="F68" t="n">
-        <v>16.519864788</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.2840693295408313</v>
       </c>
       <c r="H68" t="n">
         <v>16.519864788</v>
@@ -2984,13 +2984,13 @@
         <v>16.519864788</v>
       </c>
       <c r="E69" t="n">
+        <v>0.2840693295408313</v>
+      </c>
+      <c r="F69" t="n">
+        <v>16.519864788</v>
+      </c>
+      <c r="G69" t="n">
         <v>0.2840693295408315</v>
-      </c>
-      <c r="F69" t="n">
-        <v>16.519864788</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.2840693295408313</v>
       </c>
       <c r="H69" t="n">
         <v>16.519864788</v>
@@ -4569,22 +4569,22 @@
         <v>46023</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8173288823411099</v>
+        <v>0.815933588584339</v>
       </c>
       <c r="D112" t="n">
-        <v>22.38825160250882</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E112" t="n">
-        <v>0.815933588584339</v>
+        <v>0.7980446955356428</v>
       </c>
       <c r="F112" t="n">
         <v>29.17576040282488</v>
       </c>
       <c r="G112" t="n">
-        <v>0.7980446955356428</v>
+        <v>0.8173288823411099</v>
       </c>
       <c r="H112" t="n">
-        <v>29.17576040282488</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I112" t="n">
         <v>0.8126712660303823</v>
@@ -4606,22 +4606,22 @@
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>3.928035457318434</v>
+        <v>3.8622296382784</v>
       </c>
       <c r="D113" t="n">
-        <v>22.38825160250882</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E113" t="n">
-        <v>3.8622296382784</v>
+        <v>3.879135113112059</v>
       </c>
       <c r="F113" t="n">
         <v>29.17576040282488</v>
       </c>
       <c r="G113" t="n">
-        <v>3.879135113112059</v>
+        <v>3.928035457318434</v>
       </c>
       <c r="H113" t="n">
-        <v>29.17576040282488</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I113" t="n">
         <v>3.934229926809291</v>
@@ -4643,22 +4643,22 @@
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>4.387016591576031</v>
+        <v>3.949408456660084</v>
       </c>
       <c r="D114" t="n">
-        <v>22.38825160250882</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E114" t="n">
-        <v>3.949408456660084</v>
+        <v>3.965328962896857</v>
       </c>
       <c r="F114" t="n">
         <v>29.17576040282488</v>
       </c>
       <c r="G114" t="n">
-        <v>3.965328962896857</v>
+        <v>4.387016591576031</v>
       </c>
       <c r="H114" t="n">
-        <v>29.17576040282488</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I114" t="n">
         <v>4.401427548120806</v>
@@ -4680,22 +4680,22 @@
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>5.648880524500106</v>
+        <v>3.949408456660084</v>
       </c>
       <c r="D115" t="n">
-        <v>22.38825160250882</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E115" t="n">
-        <v>3.949408456660084</v>
+        <v>3.965328962896857</v>
       </c>
       <c r="F115" t="n">
         <v>29.17576040282488</v>
       </c>
       <c r="G115" t="n">
-        <v>3.965328962896857</v>
+        <v>5.648880524500106</v>
       </c>
       <c r="H115" t="n">
-        <v>29.17576040282488</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I115" t="n">
         <v>5.652300669671559</v>
@@ -4717,22 +4717,22 @@
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>5.752463465642453</v>
+        <v>3.609935756437439</v>
       </c>
       <c r="D116" t="n">
-        <v>22.38825160250882</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E116" t="n">
-        <v>3.609935756437439</v>
+        <v>3.587500924458367</v>
       </c>
       <c r="F116" t="n">
         <v>29.17576040282488</v>
       </c>
       <c r="G116" t="n">
-        <v>3.587500924458367</v>
+        <v>5.752463465642453</v>
       </c>
       <c r="H116" t="n">
-        <v>29.17576040282488</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I116" t="n">
         <v>5.776843553250443</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>33.24393928582102</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>61.50074829873743</v>
+        <v>33.24393928582102</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>43.24534973770062</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>61.50074829873743</v>
+        <v>43.24534973770062</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>48.05024605213596</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>61.50074829873743</v>
+        <v>48.05024605213596</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>50.80548507401782</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>61.50074829873743</v>
+        <v>50.80548507401782</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>52.57001064293669</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>61.50074829873743</v>
+        <v>52.57001064293669</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>1.880046910442136</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>3.705750567087525</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>2.526249092198093</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>3.705750567087525</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>2.836698752917273</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>3.705750567087525</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.01471779090852</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>3.705750567087525</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.128725737876166</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>3.705750567087525</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5235,10 +5235,10 @@
         <v>51502</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -5247,10 +5247,10 @@
         <v>3.03030303030303</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>53328</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -5284,10 +5284,10 @@
         <v>3.03030303030303</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>3.03030303030303</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5679,22 +5679,22 @@
         <v>46023</v>
       </c>
       <c r="C142" t="n">
+        <v>23.28695250889229</v>
+      </c>
+      <c r="D142" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E142" t="n">
+        <v>20.70736539500782</v>
+      </c>
+      <c r="F142" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G142" t="n">
         <v>35.23675532926304</v>
       </c>
-      <c r="D142" t="n">
+      <c r="H142" t="n">
         <v>43.34562491739441</v>
-      </c>
-      <c r="E142" t="n">
-        <v>23.28695250889229</v>
-      </c>
-      <c r="F142" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G142" t="n">
-        <v>20.70736539500782</v>
-      </c>
-      <c r="H142" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I142" t="n">
         <v>36.51427447413628</v>
@@ -5716,22 +5716,22 @@
         <v>47849</v>
       </c>
       <c r="C143" t="n">
+        <v>23.41282014156247</v>
+      </c>
+      <c r="D143" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E143" t="n">
+        <v>21.19061490961451</v>
+      </c>
+      <c r="F143" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G143" t="n">
         <v>35.23675532926304</v>
       </c>
-      <c r="D143" t="n">
+      <c r="H143" t="n">
         <v>60.98768095838628</v>
-      </c>
-      <c r="E143" t="n">
-        <v>23.41282014156247</v>
-      </c>
-      <c r="F143" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G143" t="n">
-        <v>21.19061490961451</v>
-      </c>
-      <c r="H143" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I143" t="n">
         <v>36.51427447413628</v>
@@ -5753,22 +5753,22 @@
         <v>49675</v>
       </c>
       <c r="C144" t="n">
+        <v>35.09786622765415</v>
+      </c>
+      <c r="D144" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E144" t="n">
+        <v>32.74837177362869</v>
+      </c>
+      <c r="F144" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G144" t="n">
         <v>45.30495501606957</v>
       </c>
-      <c r="D144" t="n">
+      <c r="H144" t="n">
         <v>71.10263572140626</v>
-      </c>
-      <c r="E144" t="n">
-        <v>35.09786622765415</v>
-      </c>
-      <c r="F144" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G144" t="n">
-        <v>32.74837177362869</v>
-      </c>
-      <c r="H144" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I144" t="n">
         <v>47.39878685835764</v>
@@ -5790,22 +5790,22 @@
         <v>51502</v>
       </c>
       <c r="C145" t="n">
+        <v>50.76838981472233</v>
+      </c>
+      <c r="D145" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E145" t="n">
+        <v>49.80524470800641</v>
+      </c>
+      <c r="F145" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G145" t="n">
         <v>48.53179471885529</v>
       </c>
-      <c r="D145" t="n">
+      <c r="H145" t="n">
         <v>77.61065910480148</v>
-      </c>
-      <c r="E145" t="n">
-        <v>50.76838981472233</v>
-      </c>
-      <c r="F145" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G145" t="n">
-        <v>49.80524470800641</v>
-      </c>
-      <c r="H145" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I145" t="n">
         <v>50.2689129275973</v>
@@ -5827,22 +5827,22 @@
         <v>53328</v>
       </c>
       <c r="C146" t="n">
+        <v>50.64252218205215</v>
+      </c>
+      <c r="D146" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E146" t="n">
+        <v>49.32199519339973</v>
+      </c>
+      <c r="F146" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G146" t="n">
         <v>48.53179471885529</v>
       </c>
-      <c r="D146" t="n">
+      <c r="H146" t="n">
         <v>82.13463969256284</v>
-      </c>
-      <c r="E146" t="n">
-        <v>50.64252218205215</v>
-      </c>
-      <c r="F146" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G146" t="n">
-        <v>49.32199519339973</v>
-      </c>
-      <c r="H146" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I146" t="n">
         <v>50.2689129275973</v>
@@ -5864,22 +5864,22 @@
         <v>46023</v>
       </c>
       <c r="C147" t="n">
+        <v>1.139805678462902</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.9647126967907047</v>
+      </c>
+      <c r="F147" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G147" t="n">
         <v>0.9745343041553989</v>
       </c>
-      <c r="D147" t="n">
+      <c r="H147" t="n">
         <v>2.335489999936831</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1.139805678462902</v>
-      </c>
-      <c r="F147" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.9647126967907047</v>
-      </c>
-      <c r="H147" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I147" t="n">
         <v>1.137324415846374</v>
@@ -5901,22 +5901,22 @@
         <v>47849</v>
       </c>
       <c r="C148" t="n">
+        <v>2.968197968865652</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.846595129892914</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G148" t="n">
         <v>2.873579449874479</v>
       </c>
-      <c r="D148" t="n">
+      <c r="H148" t="n">
         <v>3.445475894438722</v>
-      </c>
-      <c r="E148" t="n">
-        <v>2.968197968865652</v>
-      </c>
-      <c r="F148" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G148" t="n">
-        <v>2.846595129892914</v>
-      </c>
-      <c r="H148" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I148" t="n">
         <v>2.973780062832532</v>
@@ -5938,22 +5938,22 @@
         <v>49675</v>
       </c>
       <c r="C149" t="n">
+        <v>3.077189268401386</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.968646412586611</v>
+      </c>
+      <c r="F149" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G149" t="n">
         <v>2.980312443430628</v>
       </c>
-      <c r="D149" t="n">
+      <c r="H149" t="n">
         <v>4.081878878557442</v>
-      </c>
-      <c r="E149" t="n">
-        <v>3.077189268401386</v>
-      </c>
-      <c r="F149" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G149" t="n">
-        <v>2.968646412586611</v>
-      </c>
-      <c r="H149" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I149" t="n">
         <v>3.060045500198731</v>
@@ -5975,22 +5975,22 @@
         <v>51502</v>
       </c>
       <c r="C150" t="n">
+        <v>3.332371178024898</v>
+      </c>
+      <c r="D150" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E150" t="n">
+        <v>3.23971841641166</v>
+      </c>
+      <c r="F150" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G150" t="n">
         <v>3.198323525649897</v>
       </c>
-      <c r="D150" t="n">
+      <c r="H150" t="n">
         <v>4.491344427236824</v>
-      </c>
-      <c r="E150" t="n">
-        <v>3.332371178024898</v>
-      </c>
-      <c r="F150" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G150" t="n">
-        <v>3.23971841641166</v>
-      </c>
-      <c r="H150" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I150" t="n">
         <v>3.269736036639328</v>
@@ -6012,22 +6012,22 @@
         <v>53328</v>
       </c>
       <c r="C151" t="n">
+        <v>3.270842222678461</v>
+      </c>
+      <c r="D151" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3.196804501008751</v>
+      </c>
+      <c r="F151" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G151" t="n">
         <v>3.058829379926089</v>
       </c>
-      <c r="D151" t="n">
+      <c r="H151" t="n">
         <v>4.775979881729643</v>
-      </c>
-      <c r="E151" t="n">
-        <v>3.270842222678461</v>
-      </c>
-      <c r="F151" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G151" t="n">
-        <v>3.196804501008751</v>
-      </c>
-      <c r="H151" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I151" t="n">
         <v>3.202184544173091</v>
@@ -6052,19 +6052,19 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
         <v>43.34562491739441</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -6089,19 +6089,19 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
         <v>60.98768095838628</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -6126,19 +6126,19 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
         <v>71.10263572140626</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -6163,19 +6163,19 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
         <v>77.61065910480148</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -6200,19 +6200,19 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
         <v>82.13463969256284</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -6237,19 +6237,19 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
         <v>2.335489999936831</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -6274,19 +6274,19 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
         <v>3.445475894438722</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -6311,19 +6311,19 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
         <v>4.081878878557442</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
@@ -6348,19 +6348,19 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
         <v>4.491344427236824</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -6385,19 +6385,19 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
         <v>4.775979881729643</v>
-      </c>
-      <c r="E161" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -6456,19 +6456,19 @@
         <v>47849</v>
       </c>
       <c r="C163" t="n">
+        <v>0.1457412001244685</v>
+      </c>
+      <c r="D163" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.1852798886692246</v>
+      </c>
+      <c r="F163" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G163" t="n">
         <v>0.1852798886692245</v>
-      </c>
-      <c r="D163" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0.1457412001244685</v>
-      </c>
-      <c r="F163" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.1852798886692246</v>
       </c>
       <c r="H163" t="n">
         <v>143.9980922935333</v>
@@ -6493,19 +6493,19 @@
         <v>49675</v>
       </c>
       <c r="C164" t="n">
+        <v>16.14590161762709</v>
+      </c>
+      <c r="D164" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E164" t="n">
+        <v>16.35019442112522</v>
+      </c>
+      <c r="F164" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G164" t="n">
         <v>17.85889358704591</v>
-      </c>
-      <c r="D164" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="E164" t="n">
-        <v>16.14590161762709</v>
-      </c>
-      <c r="F164" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G164" t="n">
-        <v>16.35019442112522</v>
       </c>
       <c r="H164" t="n">
         <v>143.9980922935333</v>
@@ -6530,19 +6530,19 @@
         <v>51502</v>
       </c>
       <c r="C165" t="n">
+        <v>16.14590161762709</v>
+      </c>
+      <c r="D165" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E165" t="n">
+        <v>16.35019442112522</v>
+      </c>
+      <c r="F165" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G165" t="n">
         <v>18.96723235671676</v>
-      </c>
-      <c r="D165" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="E165" t="n">
-        <v>16.14590161762709</v>
-      </c>
-      <c r="F165" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G165" t="n">
-        <v>16.35019442112522</v>
       </c>
       <c r="H165" t="n">
         <v>143.9980922935333</v>
@@ -6567,19 +6567,19 @@
         <v>53328</v>
       </c>
       <c r="C166" t="n">
+        <v>30.57238326352189</v>
+      </c>
+      <c r="D166" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E166" t="n">
+        <v>31.01957579691877</v>
+      </c>
+      <c r="F166" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G166" t="n">
         <v>33.31740000858891</v>
-      </c>
-      <c r="D166" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="E166" t="n">
-        <v>30.57238326352189</v>
-      </c>
-      <c r="F166" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G166" t="n">
-        <v>31.01957579691877</v>
       </c>
       <c r="H166" t="n">
         <v>143.9980922935333</v>
@@ -6641,19 +6641,19 @@
         <v>47849</v>
       </c>
       <c r="C168" t="n">
+        <v>0.4441377190821189</v>
+      </c>
+      <c r="D168" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.4965511770593832</v>
+      </c>
+      <c r="F168" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G168" t="n">
         <v>0.460493929382878</v>
-      </c>
-      <c r="D168" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="E168" t="n">
-        <v>0.4441377190821189</v>
-      </c>
-      <c r="F168" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.4965511770593832</v>
       </c>
       <c r="H168" t="n">
         <v>8.668245024336169</v>
@@ -6678,19 +6678,19 @@
         <v>49675</v>
       </c>
       <c r="C169" t="n">
+        <v>1.335146419546385</v>
+      </c>
+      <c r="D169" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.374499894365686</v>
+      </c>
+      <c r="F169" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G169" t="n">
         <v>1.353760935826729</v>
-      </c>
-      <c r="D169" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="E169" t="n">
-        <v>1.335146419546385</v>
-      </c>
-      <c r="F169" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G169" t="n">
-        <v>1.374499894365686</v>
       </c>
       <c r="H169" t="n">
         <v>8.668245024336169</v>
@@ -6715,19 +6715,19 @@
         <v>51502</v>
       </c>
       <c r="C170" t="n">
+        <v>1.391970342055296</v>
+      </c>
+      <c r="D170" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1.484623103668534</v>
+      </c>
+      <c r="F170" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G170" t="n">
         <v>1.477678059668234</v>
-      </c>
-      <c r="D170" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1.391970342055296</v>
-      </c>
-      <c r="F170" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1.484623103668534</v>
       </c>
       <c r="H170" t="n">
         <v>8.668245024336169</v>
@@ -6752,19 +6752,19 @@
         <v>53328</v>
       </c>
       <c r="C171" t="n">
+        <v>2.291379508064205</v>
+      </c>
+      <c r="D171" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2.365417229733916</v>
+      </c>
+      <c r="F171" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G171" t="n">
         <v>2.455052416054516</v>
-      </c>
-      <c r="D171" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="E171" t="n">
-        <v>2.291379508064205</v>
-      </c>
-      <c r="F171" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G171" t="n">
-        <v>2.365417229733916</v>
       </c>
       <c r="H171" t="n">
         <v>8.668245024336169</v>
@@ -7162,19 +7162,19 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
         <v>10.40759867266749</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
@@ -7199,19 +7199,19 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
         <v>13.30840288608646</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -7236,19 +7236,19 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
         <v>15.55001026864869</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -7273,19 +7273,19 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
         <v>17.3724404785241</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
@@ -7310,19 +7310,19 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
         <v>18.9021256255163</v>
-      </c>
-      <c r="E186" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
@@ -7347,19 +7347,19 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
         <v>0.2631269806022396</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
@@ -7384,19 +7384,19 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
         <v>0.445636986926065</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
@@ -7421,19 +7421,19 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
         <v>0.5866722817847868</v>
-      </c>
-      <c r="E189" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -7458,19 +7458,19 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
         <v>0.7013341909168983</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -7495,19 +7495,19 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
         <v>0.7975774480659066</v>
-      </c>
-      <c r="E191" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
@@ -7529,22 +7529,22 @@
         <v>46023</v>
       </c>
       <c r="C192" t="n">
+        <v>19.47248582655308</v>
+      </c>
+      <c r="D192" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E192" t="n">
+        <v>20.47921905378368</v>
+      </c>
+      <c r="F192" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G192" t="n">
         <v>5.251916210523669</v>
       </c>
-      <c r="D192" t="n">
+      <c r="H192" t="n">
         <v>10.40759867266749</v>
-      </c>
-      <c r="E192" t="n">
-        <v>19.47248582655308</v>
-      </c>
-      <c r="F192" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G192" t="n">
-        <v>20.47921905378368</v>
-      </c>
-      <c r="H192" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I192" t="n">
         <v>5.251916210523669</v>
@@ -7566,22 +7566,22 @@
         <v>47849</v>
       </c>
       <c r="C193" t="n">
+        <v>19.47248582655308</v>
+      </c>
+      <c r="D193" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E193" t="n">
+        <v>20.47921905378368</v>
+      </c>
+      <c r="F193" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G193" t="n">
         <v>5.251916210523669</v>
       </c>
-      <c r="D193" t="n">
+      <c r="H193" t="n">
         <v>13.30840288608646</v>
-      </c>
-      <c r="E193" t="n">
-        <v>19.47248582655308</v>
-      </c>
-      <c r="F193" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G193" t="n">
-        <v>20.47921905378368</v>
-      </c>
-      <c r="H193" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I193" t="n">
         <v>5.326518157408448</v>
@@ -7603,22 +7603,22 @@
         <v>49675</v>
       </c>
       <c r="C194" t="n">
+        <v>19.47248582655308</v>
+      </c>
+      <c r="D194" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E194" t="n">
+        <v>20.47921905378368</v>
+      </c>
+      <c r="F194" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G194" t="n">
         <v>5.251916210523669</v>
       </c>
-      <c r="D194" t="n">
+      <c r="H194" t="n">
         <v>15.55001026864869</v>
-      </c>
-      <c r="E194" t="n">
-        <v>19.47248582655308</v>
-      </c>
-      <c r="F194" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G194" t="n">
-        <v>20.47921905378368</v>
-      </c>
-      <c r="H194" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I194" t="n">
         <v>5.326518157408448</v>
@@ -7643,19 +7643,19 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
         <v>17.3724404785241</v>
-      </c>
-      <c r="E195" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I195" t="n">
         <v>0.07460194688477868</v>
@@ -7680,19 +7680,19 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>143.9980922935333</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
         <v>18.9021256255163</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>143.9980922935333</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>143.9980922935333</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
@@ -7714,22 +7714,22 @@
         <v>46023</v>
       </c>
       <c r="C197" t="n">
+        <v>0.312005832132422</v>
+      </c>
+      <c r="D197" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="F197" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G197" t="n">
         <v>0.3543819837641523</v>
       </c>
-      <c r="D197" t="n">
+      <c r="H197" t="n">
         <v>0.2631269806022396</v>
-      </c>
-      <c r="E197" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="F197" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="H197" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I197" t="n">
         <v>0.3116721949811959</v>
@@ -7751,22 +7751,22 @@
         <v>47849</v>
       </c>
       <c r="C198" t="n">
+        <v>0.312005832132422</v>
+      </c>
+      <c r="D198" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="F198" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G198" t="n">
         <v>0.3543819837641523</v>
       </c>
-      <c r="D198" t="n">
+      <c r="H198" t="n">
         <v>0.445636986926065</v>
-      </c>
-      <c r="E198" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="F198" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="H198" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I198" t="n">
         <v>0.3116721949811959</v>
@@ -7788,22 +7788,22 @@
         <v>49675</v>
       </c>
       <c r="C199" t="n">
+        <v>0.312005832132422</v>
+      </c>
+      <c r="D199" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.3811952131278954</v>
+      </c>
+      <c r="F199" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G199" t="n">
         <v>0.3543819837641523</v>
       </c>
-      <c r="D199" t="n">
+      <c r="H199" t="n">
         <v>0.5866722817847868</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.312005832132422</v>
-      </c>
-      <c r="F199" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0.3811952131278954</v>
-      </c>
-      <c r="H199" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I199" t="n">
         <v>0.3116721949811959</v>
@@ -7828,19 +7828,19 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
         <v>0.7013341909168983</v>
-      </c>
-      <c r="E200" t="n">
-        <v>0</v>
-      </c>
-      <c r="F200" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-      <c r="H200" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -7865,19 +7865,19 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>8.668245024336169</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
         <v>0.7975774480659066</v>
-      </c>
-      <c r="E201" t="n">
-        <v>0</v>
-      </c>
-      <c r="F201" t="n">
-        <v>8.668245024336169</v>
-      </c>
-      <c r="G201" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" t="n">
-        <v>8.668245024336169</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -7914,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -8182,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>0.9010850656188373</v>
+        <v>3</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>3</v>
+        <v>0.9010850656188373</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>1.35379273555401</v>
+        <v>3</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>3</v>
+        <v>1.35379273555401</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>1.625212757373893</v>
+        <v>3</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>3</v>
+        <v>1.625212757373893</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>1.807069725934989</v>
+        <v>3</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>3</v>
+        <v>1.807069725934989</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>1.938554475864368</v>
+        <v>3</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>3</v>
+        <v>1.938554475864368</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>

--- a/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Hermenches/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,22 +465,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,25 +499,25 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>535.2234067931822</v>
+        <v>233.0039263281371</v>
       </c>
       <c r="D2" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E2" t="n">
-        <v>608.234751973933</v>
+        <v>287.3633856682319</v>
       </c>
       <c r="F2" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G2" t="n">
-        <v>642.1425063630761</v>
+        <v>233.0053317046475</v>
       </c>
       <c r="H2" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="I2" t="n">
-        <v>583.7264349594867</v>
+        <v>287.3472690972929</v>
       </c>
       <c r="J2" t="n">
         <v>136007.1489410463</v>
@@ -536,25 +536,25 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>662.9830775275</v>
+        <v>264.8123828124005</v>
       </c>
       <c r="D3" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E3" t="n">
-        <v>716.2920545273265</v>
+        <v>316.766378825012</v>
       </c>
       <c r="F3" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G3" t="n">
-        <v>777.4937979035642</v>
+        <v>265.0590452001843</v>
       </c>
       <c r="H3" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="I3" t="n">
-        <v>719.1429938608278</v>
+        <v>318.7407071782271</v>
       </c>
       <c r="J3" t="n">
         <v>136007.1489410463</v>
@@ -573,25 +573,25 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>671.0644142405843</v>
+        <v>487.5255014542958</v>
       </c>
       <c r="D4" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E4" t="n">
-        <v>722.6749827633678</v>
+        <v>492.6190629867077</v>
       </c>
       <c r="F4" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G4" t="n">
-        <v>783.0089559846165</v>
+        <v>488.6323937997587</v>
       </c>
       <c r="H4" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="I4" t="n">
-        <v>759.1268288592615</v>
+        <v>490.5575445350527</v>
       </c>
       <c r="J4" t="n">
         <v>136007.1489410463</v>
@@ -610,25 +610,25 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>934.0867024305651</v>
+        <v>493.1972731441151</v>
       </c>
       <c r="D5" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E5" t="n">
-        <v>968.4880068431048</v>
+        <v>493.9057490852763</v>
       </c>
       <c r="F5" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G5" t="n">
-        <v>917.8912060203792</v>
+        <v>494.7907961790635</v>
       </c>
       <c r="H5" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="I5" t="n">
-        <v>934.6647870538226</v>
+        <v>494.0446496802234</v>
       </c>
       <c r="J5" t="n">
         <v>136007.1489410463</v>
@@ -647,25 +647,25 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>936.3331340492535</v>
+        <v>494.8693915599139</v>
       </c>
       <c r="D6" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="E6" t="n">
-        <v>975.9242960208379</v>
+        <v>494.8570375511136</v>
       </c>
       <c r="F6" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="G6" t="n">
-        <v>917.8912060203792</v>
+        <v>495.4171387270987</v>
       </c>
       <c r="H6" t="n">
         <v>136007.1489410463</v>
       </c>
       <c r="I6" t="n">
-        <v>935.7357405940484</v>
+        <v>495.7520549802933</v>
       </c>
       <c r="J6" t="n">
         <v>136007.1489410463</v>
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -687,34 +687,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>119.5900790376851</v>
+        <v>0.4578097355147827</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>119.5900790376851</v>
+        <v>0.4578097355147827</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -724,34 +724,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>152.972602329056</v>
+        <v>0.5811061958970181</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>152.972602329056</v>
+        <v>0.5811061958970181</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -761,34 +761,34 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>167.8392704484934</v>
+        <v>0.6360153931678508</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>167.8392704484934</v>
+        <v>0.6360153931678508</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -798,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>175.9858166496768</v>
+        <v>0.6661042004811646</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>175.9858166496768</v>
+        <v>0.6661042004811646</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -835,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>204.0107234115695</v>
+        <v>0.7696126074438201</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>181.0438694811363</v>
+        <v>0.6847858323369116</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>181.0438694811363</v>
+        <v>0.6847858323369116</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="12">
@@ -1054,25 +1054,25 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08107694156772062</v>
+        <v>0.1254352500580055</v>
       </c>
       <c r="D17" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08107694156772063</v>
+        <v>0.1253735642764813</v>
       </c>
       <c r="F17" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08107694156772063</v>
+        <v>0.1257377135529412</v>
       </c>
       <c r="H17" t="n">
         <v>1.002774612488435</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08107694156772061</v>
+        <v>0.1257347343091321</v>
       </c>
       <c r="J17" t="n">
         <v>1.002774612488435</v>
@@ -1091,25 +1091,25 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08166422014075095</v>
+        <v>0.1275046703364049</v>
       </c>
       <c r="D18" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08166422014075093</v>
+        <v>0.1266540237117754</v>
       </c>
       <c r="F18" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08176476766181393</v>
+        <v>0.1270181729882353</v>
       </c>
       <c r="H18" t="n">
         <v>1.488379470582734</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08176476766181393</v>
+        <v>0.1270151937444262</v>
       </c>
       <c r="J18" t="n">
         <v>1.488379470582734</v>
@@ -1128,25 +1128,25 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08261203023901018</v>
+        <v>0.1408999811740934</v>
       </c>
       <c r="D19" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08261203023901016</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="F19" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08262513138655603</v>
+        <v>0.1406876940470589</v>
       </c>
       <c r="H19" t="n">
         <v>1.770880262100316</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08260826706804172</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="J19" t="n">
         <v>1.770880262100316</v>
@@ -1165,25 +1165,25 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08133311667316744</v>
+        <v>0.1408999811740934</v>
       </c>
       <c r="D20" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08106090679216499</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="F20" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08262513138655601</v>
+        <v>0.1406876940470588</v>
       </c>
       <c r="H20" t="n">
         <v>1.954403657032222</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08261203023901018</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="J20" t="n">
         <v>1.954403657032222</v>
@@ -1202,25 +1202,25 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08102196079476225</v>
+        <v>0.138830560895694</v>
       </c>
       <c r="D21" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08076210030521676</v>
+        <v>0.1397904668941176</v>
       </c>
       <c r="F21" t="n">
         <v>3.29226874189296</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08193730529246272</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="H21" t="n">
         <v>2.082856964215745</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08192420414491686</v>
+        <v>0.1410709263294118</v>
       </c>
       <c r="J21" t="n">
         <v>2.082856964215745</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02985187893176471</v>
+        <v>0.02657145076454228</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02985187893176471</v>
+        <v>0.02655911360823743</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02985187893176471</v>
+        <v>0.02663194346352941</v>
       </c>
       <c r="H22" t="n">
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02985187893176471</v>
+        <v>0.02663134761476758</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02993724289411765</v>
+        <v>0.02682754265160111</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02993724289411765</v>
+        <v>0.02681520549529626</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02993724289411765</v>
+        <v>0.02688803535058823</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02993724289411765</v>
+        <v>0.02688743950182641</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.03182274634274488</v>
+        <v>0.0283595928156833</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03182274634274488</v>
+        <v>0.0285169544905861</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03188228960470588</v>
+        <v>0.02821418526588237</v>
       </c>
       <c r="H24" t="n">
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03180564314823529</v>
+        <v>0.02836747817882353</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.0283595928156833</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.02851695449058609</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03376969828470588</v>
+        <v>0.02821418526588237</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.02836747817882353</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.02839378184674698</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.02851695449058609</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03376969828470588</v>
+        <v>0.02829083172235296</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03334969074745076</v>
+        <v>0.02836747817882352</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -1417,7 +1417,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1427,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         <v>0.0361830095566004</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1464,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1485,13 +1485,13 @@
         <v>0.06235215139065679</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1501,13 +1501,13 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0.08284414207442109</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1538,13 +1538,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>0.09971239592410397</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -1575,13 +1575,13 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0.1140828146841643</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -1609,25 +1609,25 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.003412443752473951</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003412443752473951</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003412443752473951</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="I32" t="n">
-        <v>0.003412443752473951</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>2.331551124703651</v>
@@ -1646,25 +1646,25 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003439290772955338</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003439290772955337</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003443887231061067</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003443887231061074</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>2.331551124703651</v>
@@ -1683,25 +1683,25 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.003497220638844078</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003497220638844079</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003510231617690212</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="I34" t="n">
-        <v>0.003493483367914731</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>2.331551124703651</v>
@@ -1720,25 +1720,25 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003904701122929663</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00391714500320406</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003941639315975926</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="I35" t="n">
-        <v>0.003846236502776852</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>2.331551124703651</v>
@@ -1757,25 +1757,25 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003918925391656758</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="E36" t="n">
-        <v>0.003930804728321693</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003973082794563049</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>2.331551124703651</v>
       </c>
       <c r="I36" t="n">
-        <v>0.003877679981363975</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>2.331551124703651</v>
@@ -1787,7 +1787,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -1797,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.02150403410002412</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.008064012787509046</v>
+        <v>0.02150403410002412</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1834,34 +1834,34 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.03771981466347649</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.01414493049880368</v>
+        <v>0.03771981466347649</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -1871,34 +1871,34 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.05079063932422077</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.01904648974658279</v>
+        <v>0.05079063932422077</v>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1908,34 +1908,34 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.06179337918200544</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.02317251719325205</v>
+        <v>0.06179337918200544</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -1945,34 +1945,34 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2822617667410714</v>
+        <v>0.7526980446428569</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.07132268642825267</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02674600741059475</v>
+        <v>0.07132268642825267</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2009,7 +2009,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2046,7 +2046,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2083,7 +2083,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -2120,7 +2120,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.002150403410002412</v>
+        <v>0.0002150403410002412</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.002150403410002412</v>
+        <v>0.0002150403410002412</v>
       </c>
       <c r="K47" t="n">
         <v>300</v>
@@ -2204,25 +2204,25 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.003771981466347649</v>
+        <v>0.0003771981466347649</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.003771981466347649</v>
+        <v>0.0003771981466347649</v>
       </c>
       <c r="K48" t="n">
         <v>300</v>
@@ -2241,25 +2241,25 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.005079063932422078</v>
+        <v>0.0005079063932422078</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.005079063932422078</v>
+        <v>0.0005079063932422078</v>
       </c>
       <c r="K49" t="n">
         <v>300</v>
@@ -2275,28 +2275,28 @@
         <v>51502</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02812259312039597</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0270196970049451</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.006179337918200545</v>
+        <v>0.0006179337918200545</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.006179337918200545</v>
+        <v>0.0006179337918200545</v>
       </c>
       <c r="K50" t="n">
         <v>300</v>
@@ -2312,28 +2312,28 @@
         <v>53328</v>
       </c>
       <c r="C51" t="n">
-        <v>0.02812259312039597</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0270196970049451</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0752698044642857</v>
+        <v>0.00752698044642857</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.007132268642825267</v>
+        <v>0.0007132268642825267</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.007132268642825267</v>
+        <v>0.0007132268642825267</v>
       </c>
       <c r="K51" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2352,34 +2352,34 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>0.1290242046001447</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>0.1290242046001447</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -2389,34 +2389,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>0.2263188879808589</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>0.2263188879808589</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2426,108 +2426,108 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>0.3047438359453247</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>0.3047438359453247</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>0.3707602750920327</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>0.3707602750920327</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>4.516188267857142</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>0.427936118569516</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>0.427936118569516</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2558,13 +2558,13 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2595,13 +2595,13 @@
         <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2632,13 +2632,13 @@
         <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2669,13 +2669,13 @@
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2706,568 +2706,568 @@
         <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1490189445946008</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1365965460824477</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1490189445946008</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1365965460824477</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1490189445946008</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1365965460824477</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>0.07659865849999996</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>0.07659865849999996</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1148979877499999</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1.2868574628</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4066972391978736</v>
       </c>
       <c r="D67" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2840693295408313</v>
+        <v>0.4076345394501667</v>
       </c>
       <c r="F67" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4066972391978737</v>
       </c>
       <c r="H67" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4076345394501668</v>
       </c>
       <c r="J67" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K67" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="D68" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2840693295408313</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="F68" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="H68" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="J68" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K68" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="D69" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2840693295408313</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="F69" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="H69" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2840693295408315</v>
+        <v>0.4212926217499999</v>
       </c>
       <c r="J69" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K69" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3362538825190295</v>
       </c>
       <c r="D70" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3361153709787713</v>
       </c>
       <c r="F70" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3592893458021262</v>
       </c>
       <c r="H70" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3583520455498331</v>
       </c>
       <c r="J70" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K70" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3383463308539388</v>
       </c>
       <c r="D71" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.3382004128356805</v>
       </c>
       <c r="F71" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.34469396325</v>
       </c>
       <c r="H71" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1537876479167835</v>
+        <v>0.34469396325</v>
       </c>
       <c r="J71" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K71" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>0.5786397036630899</v>
       </c>
       <c r="D72" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.5720855893761395</v>
       </c>
       <c r="F72" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>0.6107764499999999</v>
       </c>
       <c r="H72" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>0.6104599053452815</v>
       </c>
       <c r="J72" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>0.5786397036630899</v>
       </c>
       <c r="D73" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>0.5720855893761395</v>
       </c>
       <c r="F73" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>0.6107764499999999</v>
       </c>
       <c r="H73" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.6104599053452815</v>
       </c>
       <c r="J73" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K73" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>2.985647979274763</v>
       </c>
       <c r="D74" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2.898033284205732</v>
       </c>
       <c r="F74" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2.96233978558986</v>
       </c>
       <c r="H74" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>2.953849235975576</v>
       </c>
       <c r="J74" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K74" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2.949103651636984</v>
       </c>
       <c r="D75" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2.977407197818706</v>
       </c>
       <c r="F75" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2.970727078515849</v>
       </c>
       <c r="H75" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>2.992706315115167</v>
       </c>
       <c r="J75" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K75" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>3.051375259577606</v>
       </c>
       <c r="D76" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>3.052497410557567</v>
       </c>
       <c r="F76" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2.996371204343954</v>
       </c>
       <c r="H76" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3.017922516443003</v>
       </c>
       <c r="J76" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K76" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -3277,34 +3277,34 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K77" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3314,34 +3314,34 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K78" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -3351,34 +3351,34 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K79" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3388,34 +3388,34 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K80" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -3425,34 +3425,34 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K81" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3462,34 +3462,34 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K82" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -3499,34 +3499,34 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K83" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -3536,34 +3536,34 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K84" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -3573,34 +3573,34 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K85" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -3610,34 +3610,34 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K86" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -3647,34 +3647,34 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K87" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -3684,34 +3684,34 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K88" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -3721,34 +3721,34 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K89" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3758,34 +3758,34 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K90" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -3795,182 +3795,182 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K91" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.19501046633691</v>
       </c>
       <c r="D92" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.2015645806238603</v>
       </c>
       <c r="F92" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.1628737200000001</v>
       </c>
       <c r="H92" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>0.1631902646547184</v>
       </c>
       <c r="J92" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K92" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.2357288963369101</v>
       </c>
       <c r="D93" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.2422830106238603</v>
       </c>
       <c r="F93" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.20359215</v>
       </c>
       <c r="H93" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>0.203592149999994</v>
       </c>
       <c r="J93" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K93" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.2357288963369101</v>
       </c>
       <c r="D94" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>0.2422830106238603</v>
       </c>
       <c r="F94" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>0.248941755</v>
       </c>
       <c r="H94" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>0.248941754999994</v>
       </c>
       <c r="J94" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K94" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.04071843000000011</v>
       </c>
       <c r="D95" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>0.04071842999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.2082233250000122</v>
       </c>
       <c r="H95" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>0.2082233250000001</v>
       </c>
       <c r="J95" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K95" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -3980,34 +3980,34 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>0.1675048950000122</v>
       </c>
       <c r="H96" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.1678214396547245</v>
       </c>
       <c r="J96" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K96" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -4017,34 +4017,34 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K97" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4054,34 +4054,34 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K98" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -4091,34 +4091,34 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K99" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4128,34 +4128,34 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K100" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -4165,34 +4165,34 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K101" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -4202,34 +4202,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K102" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -4239,34 +4239,34 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K103" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -4276,34 +4276,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K104" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -4313,34 +4313,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K105" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4350,34 +4350,34 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1.2868574628</v>
+        <v>16.519864788</v>
       </c>
       <c r="K106" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K107" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4424,34 +4424,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K108" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -4461,34 +4461,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K109" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4498,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K110" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4535,404 +4535,404 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>16.519864788</v>
+        <v>1.2868574628</v>
       </c>
       <c r="K111" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C112" t="n">
-        <v>0.815933588584339</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7980446955356428</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8173288823411099</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8126712660303823</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>3.8622296382784</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="E113" t="n">
-        <v>3.879135113112059</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="G113" t="n">
-        <v>3.928035457318434</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="I113" t="n">
-        <v>3.934229926809291</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>3.949408456660084</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="E114" t="n">
-        <v>3.965328962896857</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="G114" t="n">
-        <v>4.387016591576031</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="I114" t="n">
-        <v>4.401427548120806</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>3.949408456660084</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="E115" t="n">
-        <v>3.965328962896857</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="G115" t="n">
-        <v>5.648880524500106</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="I115" t="n">
-        <v>5.652300669671559</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>3.609935756437439</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="E116" t="n">
-        <v>3.587500924458367</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>29.17576040282488</v>
+        <v>16.519864788</v>
       </c>
       <c r="G116" t="n">
-        <v>5.752463465642453</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="I116" t="n">
-        <v>5.776843553250443</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>22.38825160250882</v>
+        <v>16.519864788</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.9221222292197564</v>
       </c>
       <c r="D117" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>0.8956200888673126</v>
       </c>
       <c r="F117" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>0.7056568805935669</v>
       </c>
       <c r="H117" t="n">
-        <v>33.24393928582102</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>0.6825012204210483</v>
       </c>
       <c r="J117" t="n">
-        <v>33.24393928582102</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K117" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>3.799012422655354</v>
       </c>
       <c r="D118" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>3.765190726882421</v>
       </c>
       <c r="F118" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>3.857053525831566</v>
       </c>
       <c r="H118" t="n">
-        <v>43.24534973770062</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>3.848270186643684</v>
       </c>
       <c r="J118" t="n">
-        <v>43.24534973770062</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>3.799012422655355</v>
       </c>
       <c r="D119" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>3.765190726882421</v>
       </c>
       <c r="F119" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>4.40098745566581</v>
       </c>
       <c r="H119" t="n">
-        <v>48.05024605213596</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>4.400998743770634</v>
       </c>
       <c r="J119" t="n">
-        <v>48.05024605213596</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>3.799012422655355</v>
       </c>
       <c r="D120" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>3.765190726882422</v>
       </c>
       <c r="F120" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>5.448257534994233</v>
       </c>
       <c r="H120" t="n">
-        <v>50.80548507401782</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>5.448257534994233</v>
       </c>
       <c r="J120" t="n">
-        <v>50.80548507401782</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>2.876890193435598</v>
       </c>
       <c r="D121" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>2.869570638015109</v>
       </c>
       <c r="F121" t="n">
-        <v>61.50074829873743</v>
+        <v>29.17576040282488</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>5.71261242218619</v>
       </c>
       <c r="H121" t="n">
-        <v>52.57001064293669</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>5.688881223001301</v>
       </c>
       <c r="J121" t="n">
-        <v>52.57001064293669</v>
+        <v>22.38825160250882</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -4942,34 +4942,34 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1.880046910442136</v>
+        <v>33.24393928582102</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1.880046910442136</v>
+        <v>33.24393928582102</v>
       </c>
       <c r="K122" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -4979,34 +4979,34 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>2.526249092198093</v>
+        <v>43.24534973770062</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>2.526249092198093</v>
+        <v>43.24534973770062</v>
       </c>
       <c r="K123" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -5016,34 +5016,34 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>2.836698752917273</v>
+        <v>48.05024605213596</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>2.836698752917273</v>
+        <v>48.05024605213596</v>
       </c>
       <c r="K124" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -5053,34 +5053,34 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>3.01471779090852</v>
+        <v>50.80548507401782</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>3.01471779090852</v>
+        <v>50.80548507401782</v>
       </c>
       <c r="K125" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -5090,34 +5090,34 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>3.705750567087525</v>
+        <v>61.50074829873743</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>3.128725737876166</v>
+        <v>52.57001064293669</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>3.128725737876166</v>
+        <v>52.57001064293669</v>
       </c>
       <c r="K126" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,34 +5127,34 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1.880046910442136</v>
       </c>
       <c r="K127" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -5164,34 +5164,34 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>2.526249092198093</v>
       </c>
       <c r="K128" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -5201,108 +5201,108 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>2.836698752917273</v>
       </c>
       <c r="K129" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>3.01471779090852</v>
       </c>
       <c r="K130" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>3.03030303030303</v>
+        <v>3.705750567087525</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>3.128725737876166</v>
       </c>
       <c r="K131" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,34 +5312,34 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -5349,34 +5349,34 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -5386,108 +5386,108 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>143.9980922935333</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>143.9980922935333</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -5497,34 +5497,34 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K137" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -5534,34 +5534,34 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K138" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -5571,34 +5571,34 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K139" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -5608,34 +5608,34 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K140" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -5645,589 +5645,589 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K141" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>23.28695250889229</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E142" t="n">
-        <v>20.70736539500782</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G142" t="n">
-        <v>35.23675532926304</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>43.34562491739441</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I142" t="n">
-        <v>36.51427447413628</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>43.34562491739441</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K142" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>23.41282014156247</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E143" t="n">
-        <v>21.19061490961451</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G143" t="n">
-        <v>35.23675532926304</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>60.98768095838628</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I143" t="n">
-        <v>36.51427447413628</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>60.98768095838628</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K143" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>35.09786622765415</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E144" t="n">
-        <v>32.74837177362869</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G144" t="n">
-        <v>45.30495501606957</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>71.10263572140626</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I144" t="n">
-        <v>47.39878685835764</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>71.10263572140626</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K144" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>50.76838981472233</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E145" t="n">
-        <v>49.80524470800641</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G145" t="n">
-        <v>48.53179471885529</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>77.61065910480148</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I145" t="n">
-        <v>50.2689129275973</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>77.61065910480148</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K145" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>50.64252218205215</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E146" t="n">
-        <v>49.32199519339973</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G146" t="n">
-        <v>48.53179471885529</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>82.13463969256284</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I146" t="n">
-        <v>50.2689129275973</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>82.13463969256284</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K146" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>1.139805678462902</v>
+        <v>19.89073522140448</v>
       </c>
       <c r="D147" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E147" t="n">
-        <v>0.9647126967907047</v>
+        <v>16.57711178654765</v>
       </c>
       <c r="F147" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G147" t="n">
-        <v>0.9745343041553989</v>
+        <v>19.74703137141075</v>
       </c>
       <c r="H147" t="n">
-        <v>2.335489999936831</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="I147" t="n">
-        <v>1.137324415846374</v>
+        <v>16.78117551532304</v>
       </c>
       <c r="J147" t="n">
-        <v>2.335489999936831</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="K147" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>2.968197968865652</v>
+        <v>24.5224671151576</v>
       </c>
       <c r="D148" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E148" t="n">
-        <v>2.846595129892914</v>
+        <v>22.10546118843582</v>
       </c>
       <c r="F148" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G148" t="n">
-        <v>2.873579449874479</v>
+        <v>24.37876326516386</v>
       </c>
       <c r="H148" t="n">
-        <v>3.445475894438722</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="I148" t="n">
-        <v>2.973780062832532</v>
+        <v>22.3600814569414</v>
       </c>
       <c r="J148" t="n">
-        <v>3.445475894438722</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="K148" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>3.077189268401386</v>
+        <v>38.24800826695631</v>
       </c>
       <c r="D149" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E149" t="n">
-        <v>2.968646412586611</v>
+        <v>37.51569182628239</v>
       </c>
       <c r="F149" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G149" t="n">
-        <v>2.980312443430628</v>
+        <v>37.89470635452086</v>
       </c>
       <c r="H149" t="n">
-        <v>4.081878878557442</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="I149" t="n">
-        <v>3.060045500198731</v>
+        <v>37.58050463414299</v>
       </c>
       <c r="J149" t="n">
-        <v>4.081878878557442</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="K149" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>3.332371178024898</v>
+        <v>53.27027310749652</v>
       </c>
       <c r="D150" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E150" t="n">
-        <v>3.23971841641166</v>
+        <v>49.9247631875192</v>
       </c>
       <c r="F150" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G150" t="n">
-        <v>3.198323525649897</v>
+        <v>50.05948663943438</v>
       </c>
       <c r="H150" t="n">
-        <v>4.491344427236824</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="I150" t="n">
-        <v>3.269736036639328</v>
+        <v>48.99427303087168</v>
       </c>
       <c r="J150" t="n">
-        <v>4.491344427236824</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="K150" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>3.270842222678461</v>
+        <v>50.9831110471118</v>
       </c>
       <c r="D151" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E151" t="n">
-        <v>3.196804501008751</v>
+        <v>49.44866938326619</v>
       </c>
       <c r="F151" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G151" t="n">
-        <v>3.058829379926089</v>
+        <v>49.49790940100971</v>
       </c>
       <c r="H151" t="n">
-        <v>4.775979881729643</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="I151" t="n">
-        <v>3.202184544173091</v>
+        <v>48.24209800351358</v>
       </c>
       <c r="J151" t="n">
-        <v>4.775979881729643</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="K151" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1.23962336180346</v>
       </c>
       <c r="D152" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1.022919609786701</v>
       </c>
       <c r="F152" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1.243085274532566</v>
       </c>
       <c r="H152" t="n">
-        <v>43.34562491739441</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1.035931665466861</v>
       </c>
       <c r="J152" t="n">
-        <v>43.34562491739441</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="K152" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>2.959425936718283</v>
       </c>
       <c r="D153" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>2.844658458035571</v>
       </c>
       <c r="F153" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>2.96288784944739</v>
       </c>
       <c r="H153" t="n">
-        <v>60.98768095838628</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>2.850047957587999</v>
       </c>
       <c r="J153" t="n">
-        <v>60.98768095838628</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="K153" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>3.005339303355403</v>
       </c>
       <c r="D154" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>2.844658458035571</v>
       </c>
       <c r="F154" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>3.011251625731855</v>
       </c>
       <c r="H154" t="n">
-        <v>71.10263572140626</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>2.853257428819573</v>
       </c>
       <c r="J154" t="n">
-        <v>71.10263572140626</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="K154" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>3.217930792737935</v>
       </c>
       <c r="D155" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>3.190693697497855</v>
       </c>
       <c r="F155" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>3.187232003258527</v>
       </c>
       <c r="H155" t="n">
-        <v>77.61065910480148</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>3.173232504592503</v>
       </c>
       <c r="J155" t="n">
-        <v>77.61065910480148</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="K155" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>3.221959136115379</v>
       </c>
       <c r="D156" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>3.193717894773948</v>
       </c>
       <c r="F156" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>3.173486991488915</v>
       </c>
       <c r="H156" t="n">
-        <v>82.13463969256284</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>3.011251625731854</v>
       </c>
       <c r="J156" t="n">
-        <v>82.13463969256284</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="K156" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -6237,34 +6237,34 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>2.335489999936831</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>2.335489999936831</v>
+        <v>43.34562491739441</v>
       </c>
       <c r="K157" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
@@ -6274,34 +6274,34 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>3.445475894438722</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>3.445475894438722</v>
+        <v>60.98768095838628</v>
       </c>
       <c r="K158" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
@@ -6311,34 +6311,34 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>4.081878878557442</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>4.081878878557442</v>
+        <v>71.10263572140626</v>
       </c>
       <c r="K159" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
@@ -6348,34 +6348,34 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>4.491344427236824</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>4.491344427236824</v>
+        <v>77.61065910480148</v>
       </c>
       <c r="K160" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
@@ -6385,34 +6385,34 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>4.775979881729643</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>4.775979881729643</v>
+        <v>82.13463969256284</v>
       </c>
       <c r="K161" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -6422,182 +6422,182 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>143.9980922935333</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>143.9980922935333</v>
+        <v>2.335489999936831</v>
       </c>
       <c r="K162" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1457412001244685</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1852798886692246</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1852798886692245</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>143.9980922935333</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1173931149123253</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>143.9980922935333</v>
+        <v>3.445475894438722</v>
       </c>
       <c r="K163" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>16.14590161762709</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E164" t="n">
-        <v>16.35019442112522</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G164" t="n">
-        <v>17.85889358704591</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>143.9980922935333</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="I164" t="n">
-        <v>16.21435565446135</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>143.9980922935333</v>
+        <v>4.081878878557442</v>
       </c>
       <c r="K164" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>16.14590161762709</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E165" t="n">
-        <v>16.35019442112522</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G165" t="n">
-        <v>18.96723235671676</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>143.9980922935333</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="I165" t="n">
-        <v>16.72398495321817</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>143.9980922935333</v>
+        <v>4.491344427236824</v>
       </c>
       <c r="K165" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>30.57238326352189</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E166" t="n">
-        <v>31.01957579691877</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G166" t="n">
-        <v>33.31740000858891</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>143.9980922935333</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="I166" t="n">
-        <v>31.12513057682317</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>143.9980922935333</v>
+        <v>4.775979881729643</v>
       </c>
       <c r="K166" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6607,182 +6607,182 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K167" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4441377190821189</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E168" t="n">
-        <v>0.4965511770593832</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G168" t="n">
-        <v>0.460493929382878</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I168" t="n">
-        <v>0.403622706582872</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K168" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>1.335146419546385</v>
+        <v>4.490815690608928</v>
       </c>
       <c r="D169" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E169" t="n">
-        <v>1.374499894365686</v>
+        <v>5.039731396477708</v>
       </c>
       <c r="F169" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G169" t="n">
-        <v>1.353760935826729</v>
+        <v>4.695716724162668</v>
       </c>
       <c r="H169" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I169" t="n">
-        <v>1.317357269216672</v>
+        <v>5.1873479468803</v>
       </c>
       <c r="J169" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K169" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>1.391970342055296</v>
+        <v>6.699276850392597</v>
       </c>
       <c r="D170" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E170" t="n">
-        <v>1.484623103668534</v>
+        <v>10.03442847189609</v>
       </c>
       <c r="F170" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G170" t="n">
-        <v>1.477678059668234</v>
+        <v>9.905366289566738</v>
       </c>
       <c r="H170" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I170" t="n">
-        <v>1.419338927757271</v>
+        <v>10.97328425803141</v>
       </c>
       <c r="J170" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K170" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>2.291379508064205</v>
+        <v>19.87417129828994</v>
       </c>
       <c r="D171" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E171" t="n">
-        <v>2.365417229733916</v>
+        <v>21.40226043038036</v>
       </c>
       <c r="F171" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G171" t="n">
-        <v>2.455052416054516</v>
+        <v>21.3491259399876</v>
       </c>
       <c r="H171" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I171" t="n">
-        <v>2.324770630885982</v>
+        <v>22.60011955137323</v>
       </c>
       <c r="J171" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K171" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -6792,34 +6792,34 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K172" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -6829,145 +6829,145 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K173" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>0.3651362479664485</v>
       </c>
       <c r="D174" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>0.3920130017816497</v>
       </c>
       <c r="F174" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>0.3626858383191034</v>
       </c>
       <c r="H174" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>0.4046930887357992</v>
       </c>
       <c r="J174" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K174" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>0.3651362479664485</v>
       </c>
       <c r="D175" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>0.3920130017816497</v>
       </c>
       <c r="F175" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>0.392949400818234</v>
       </c>
       <c r="H175" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>0.4046930887357992</v>
       </c>
       <c r="J175" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K175" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>0.9874760527148405</v>
       </c>
       <c r="D176" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>1.015356952631393</v>
       </c>
       <c r="F176" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1.033062560713682</v>
       </c>
       <c r="H176" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>1.195699313958054</v>
       </c>
       <c r="J176" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K176" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,34 +6977,34 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K177" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -7014,34 +7014,34 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K178" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -7051,34 +7051,34 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K179" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K180" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -7125,34 +7125,34 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K181" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>10.40759867266749</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>10.40759867266749</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K182" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>13.30840288608646</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>13.30840288608646</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K183" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>15.55001026864869</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>15.55001026864869</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K184" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>17.3724404785241</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>17.3724404785241</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K185" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,34 +7310,34 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>18.9021256255163</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>18.9021256255163</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K186" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -7347,34 +7347,34 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>0.2631269806022396</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0.2631269806022396</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K187" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -7384,34 +7384,34 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0.445636986926065</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0.445636986926065</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K188" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -7421,34 +7421,34 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0.5866722817847868</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0.5866722817847868</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K189" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -7458,34 +7458,34 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7013341909168983</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0.7013341909168983</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K190" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,145 +7495,145 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>0.7975774480659066</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>0.7975774480659066</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K191" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>19.47248582655308</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E192" t="n">
-        <v>20.47921905378368</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G192" t="n">
-        <v>5.251916210523669</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>10.40759867266749</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I192" t="n">
-        <v>5.251916210523669</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>10.40759867266749</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K192" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>19.47248582655308</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E193" t="n">
-        <v>20.47921905378368</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G193" t="n">
-        <v>5.251916210523669</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>13.30840288608646</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I193" t="n">
-        <v>5.326518157408448</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>13.30840288608646</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K193" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>19.47248582655308</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E194" t="n">
-        <v>20.47921905378368</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G194" t="n">
-        <v>5.251916210523669</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>15.55001026864869</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I194" t="n">
-        <v>5.326518157408448</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>15.55001026864869</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K194" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -7643,34 +7643,34 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>17.3724404785241</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I195" t="n">
-        <v>0.07460194688477868</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>17.3724404785241</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K195" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -7680,145 +7680,145 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>143.9980922935333</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>18.9021256255163</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>18.9021256255163</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="K196" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0.312005832132422</v>
+        <v>15.23072600032384</v>
       </c>
       <c r="D197" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3811952131278954</v>
+        <v>15.4037684366552</v>
       </c>
       <c r="F197" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3543819837641523</v>
+        <v>15.37442985031758</v>
       </c>
       <c r="H197" t="n">
-        <v>0.2631269806022396</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3116721949811959</v>
+        <v>15.19970470787981</v>
       </c>
       <c r="J197" t="n">
-        <v>0.2631269806022396</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K197" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0.312005832132422</v>
+        <v>15.23072600032384</v>
       </c>
       <c r="D198" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3811952131278954</v>
+        <v>15.4037684366552</v>
       </c>
       <c r="F198" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3543819837641523</v>
+        <v>15.37442985031758</v>
       </c>
       <c r="H198" t="n">
-        <v>0.445636986926065</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3116721949811959</v>
+        <v>15.19970470787981</v>
       </c>
       <c r="J198" t="n">
-        <v>0.445636986926065</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K198" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0.312005832132422</v>
+        <v>15.23072600032384</v>
       </c>
       <c r="D199" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E199" t="n">
-        <v>0.3811952131278954</v>
+        <v>15.4037684366552</v>
       </c>
       <c r="F199" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3543819837641523</v>
+        <v>15.37442985031758</v>
       </c>
       <c r="H199" t="n">
-        <v>0.5866722817847868</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3116721949811959</v>
+        <v>15.19970470787981</v>
       </c>
       <c r="J199" t="n">
-        <v>0.5866722817847868</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K199" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -7828,34 +7828,34 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7013341909168983</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0.7013341909168983</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K200" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7865,139 +7865,145 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>8.668245024336169</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>0.7975774480659066</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>0.7975774480659066</v>
+        <v>143.9980922935333</v>
       </c>
       <c r="K201" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="D202" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="H202" t="n">
-        <v>0.9010850656188373</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="J202" t="n">
-        <v>0.9010850656188373</v>
-      </c>
-      <c r="K202" t="inlineStr"/>
+        <v>8.668245024336169</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="H203" t="n">
-        <v>1.35379273555401</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="J203" t="n">
-        <v>1.35379273555401</v>
-      </c>
-      <c r="K203" t="inlineStr"/>
+        <v>8.668245024336169</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>0.2462241239148233</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>0.3536650676143267</v>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>0.2427622111857164</v>
       </c>
       <c r="H204" t="n">
-        <v>1.625212757373893</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>0.340653011934167</v>
       </c>
       <c r="J204" t="n">
-        <v>1.625212757373893</v>
-      </c>
-      <c r="K204" t="inlineStr"/>
+        <v>8.668245024336169</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -8007,32 +8013,34 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>1.807069725934989</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>1.807069725934989</v>
-      </c>
-      <c r="K205" t="inlineStr"/>
+        <v>8.668245024336169</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8042,32 +8050,34 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>1.938554475864368</v>
+        <v>8.668245024336169</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>1.938554475864368</v>
-      </c>
-      <c r="K206" t="inlineStr"/>
+        <v>8.668245024336169</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -8102,7 +8112,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -8137,7 +8147,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -8172,7 +8182,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8207,7 +8217,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8242,7 +8252,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8277,7 +8287,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8312,7 +8322,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8347,7 +8357,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8382,7 +8392,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8413,6 +8423,181 @@
         <v>1.938554475864368</v>
       </c>
       <c r="K216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>3</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.9010850656188373</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.9010850656188373</v>
+      </c>
+      <c r="K217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>47849</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1.35379273555401</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1.35379273555401</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>49675</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>3</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1.625212757373893</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1.625212757373893</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>51502</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>3</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1.807069725934989</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1.807069725934989</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>53328</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>3</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1.938554475864368</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1.938554475864368</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
